--- a/bareme_couts.xlsx
+++ b/bareme_couts.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\hateta72d\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{56EEB52F-4776-4FB2-BBD0-B78F447B5DFD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C3B7C0C3-33B3-4CB0-A088-F94481C122F3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="22932" yWindow="-2136" windowWidth="23256" windowHeight="13896" firstSheet="9" activeTab="15" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="22932" yWindow="-2136" windowWidth="23256" windowHeight="13896" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Lisez-moi" sheetId="1" r:id="rId1"/>
@@ -2420,18 +2420,18 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:B11"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="70.875" customWidth="1"/>
     <col min="2" max="2" width="20.875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>1</v>
       </c>
@@ -2439,42 +2439,42 @@
         <v>2</v>
       </c>
     </row>
-    <row r="4" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="5" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="6" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="7" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="8" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="9" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="10" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="11" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>10</v>
       </c>
@@ -2490,13 +2490,13 @@
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0900-000000000000}">
   <dimension ref="A1:D4"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="60.875" customWidth="1"/>
     <col min="2" max="4" width="20.875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>465</v>
       </c>
@@ -2510,7 +2510,7 @@
         <v>467</v>
       </c>
     </row>
-    <row r="2" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>468</v>
       </c>
@@ -2521,7 +2521,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>469</v>
       </c>
@@ -2532,7 +2532,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>470</v>
       </c>
@@ -2551,13 +2551,13 @@
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0A00-000000000000}">
   <dimension ref="A1:E117"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="60.875" customWidth="1"/>
     <col min="2" max="5" width="20.875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>11</v>
       </c>
@@ -2574,7 +2574,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="2" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>471</v>
       </c>
@@ -2591,7 +2591,7 @@
         <v>139</v>
       </c>
     </row>
-    <row r="3" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>472</v>
       </c>
@@ -2608,7 +2608,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="4" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>473</v>
       </c>
@@ -2625,7 +2625,7 @@
         <v>122</v>
       </c>
     </row>
-    <row r="5" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>474</v>
       </c>
@@ -2642,7 +2642,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="6" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>475</v>
       </c>
@@ -2659,7 +2659,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="7" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>476</v>
       </c>
@@ -2676,7 +2676,7 @@
         <v>131</v>
       </c>
     </row>
-    <row r="8" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>477</v>
       </c>
@@ -2693,7 +2693,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="9" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>478</v>
       </c>
@@ -2710,7 +2710,7 @@
         <v>124</v>
       </c>
     </row>
-    <row r="10" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>479</v>
       </c>
@@ -2727,7 +2727,7 @@
         <v>124</v>
       </c>
     </row>
-    <row r="11" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>480</v>
       </c>
@@ -2744,7 +2744,7 @@
         <v>119</v>
       </c>
     </row>
-    <row r="12" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>481</v>
       </c>
@@ -2761,7 +2761,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="13" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>482</v>
       </c>
@@ -2778,7 +2778,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="14" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>482</v>
       </c>
@@ -2795,7 +2795,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="15" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>483</v>
       </c>
@@ -2812,7 +2812,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="16" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>484</v>
       </c>
@@ -2829,7 +2829,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="17" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>485</v>
       </c>
@@ -2846,7 +2846,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="18" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>486</v>
       </c>
@@ -2863,7 +2863,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="19" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>487</v>
       </c>
@@ -2880,7 +2880,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="20" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>488</v>
       </c>
@@ -2897,7 +2897,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="21" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>489</v>
       </c>
@@ -2914,7 +2914,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="22" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>486</v>
       </c>
@@ -2931,7 +2931,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="23" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>487</v>
       </c>
@@ -2948,7 +2948,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="24" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>490</v>
       </c>
@@ -2965,7 +2965,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="25" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>491</v>
       </c>
@@ -2982,7 +2982,7 @@
         <v>236</v>
       </c>
     </row>
-    <row r="26" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>492</v>
       </c>
@@ -2999,7 +2999,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="27" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>493</v>
       </c>
@@ -3016,7 +3016,7 @@
         <v>126</v>
       </c>
     </row>
-    <row r="28" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
         <v>494</v>
       </c>
@@ -3033,7 +3033,7 @@
         <v>158</v>
       </c>
     </row>
-    <row r="29" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
         <v>495</v>
       </c>
@@ -3050,7 +3050,7 @@
         <v>127.3</v>
       </c>
     </row>
-    <row r="30" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
         <v>496</v>
       </c>
@@ -3067,7 +3067,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="31" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
         <v>497</v>
       </c>
@@ -3084,7 +3084,7 @@
         <v>77.3</v>
       </c>
     </row>
-    <row r="32" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
         <v>498</v>
       </c>
@@ -3101,7 +3101,7 @@
         <v>671</v>
       </c>
     </row>
-    <row r="33" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
         <v>499</v>
       </c>
@@ -3118,7 +3118,7 @@
         <v>445</v>
       </c>
     </row>
-    <row r="34" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
         <v>500</v>
       </c>
@@ -3135,7 +3135,7 @@
         <v>490</v>
       </c>
     </row>
-    <row r="35" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
         <v>501</v>
       </c>
@@ -3152,7 +3152,7 @@
         <v>69.099999999999994</v>
       </c>
     </row>
-    <row r="36" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
         <v>502</v>
       </c>
@@ -3169,7 +3169,7 @@
         <v>58.5</v>
       </c>
     </row>
-    <row r="37" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
         <v>503</v>
       </c>
@@ -3186,7 +3186,7 @@
         <v>66.3</v>
       </c>
     </row>
-    <row r="38" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
         <v>504</v>
       </c>
@@ -3203,7 +3203,7 @@
         <v>62.4</v>
       </c>
     </row>
-    <row r="39" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
         <v>505</v>
       </c>
@@ -3220,7 +3220,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="40" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
         <v>506</v>
       </c>
@@ -3237,7 +3237,7 @@
         <v>40.299999999999997</v>
       </c>
     </row>
-    <row r="41" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
         <v>507</v>
       </c>
@@ -3254,7 +3254,7 @@
         <v>44.9</v>
       </c>
     </row>
-    <row r="42" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
         <v>508</v>
       </c>
@@ -3271,7 +3271,7 @@
         <v>38.1</v>
       </c>
     </row>
-    <row r="43" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
         <v>509</v>
       </c>
@@ -3288,7 +3288,7 @@
         <v>29.6</v>
       </c>
     </row>
-    <row r="44" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
         <v>509</v>
       </c>
@@ -3305,7 +3305,7 @@
         <v>32.9</v>
       </c>
     </row>
-    <row r="45" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
         <v>510</v>
       </c>
@@ -3322,7 +3322,7 @@
         <v>32.1</v>
       </c>
     </row>
-    <row r="46" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
         <v>511</v>
       </c>
@@ -3339,7 +3339,7 @@
         <v>24.3</v>
       </c>
     </row>
-    <row r="47" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
         <v>512</v>
       </c>
@@ -3356,7 +3356,7 @@
         <v>35.1</v>
       </c>
     </row>
-    <row r="48" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
         <v>513</v>
       </c>
@@ -3373,7 +3373,7 @@
         <v>22.4</v>
       </c>
     </row>
-    <row r="49" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
         <v>514</v>
       </c>
@@ -3390,7 +3390,7 @@
         <v>20.6</v>
       </c>
     </row>
-    <row r="50" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
         <v>515</v>
       </c>
@@ -3407,7 +3407,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="51" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
         <v>516</v>
       </c>
@@ -3424,7 +3424,7 @@
         <v>20.8</v>
       </c>
     </row>
-    <row r="52" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
         <v>517</v>
       </c>
@@ -3441,7 +3441,7 @@
         <v>26.9</v>
       </c>
     </row>
-    <row r="53" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
         <v>518</v>
       </c>
@@ -3458,7 +3458,7 @@
         <v>22.4</v>
       </c>
     </row>
-    <row r="54" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
         <v>519</v>
       </c>
@@ -3475,7 +3475,7 @@
         <v>26.4</v>
       </c>
     </row>
-    <row r="55" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
         <v>520</v>
       </c>
@@ -3492,7 +3492,7 @@
         <v>23.6</v>
       </c>
     </row>
-    <row r="56" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
         <v>521</v>
       </c>
@@ -3509,7 +3509,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="57" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
         <v>522</v>
       </c>
@@ -3526,7 +3526,7 @@
         <v>17.100000000000001</v>
       </c>
     </row>
-    <row r="58" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
         <v>523</v>
       </c>
@@ -3543,7 +3543,7 @@
         <v>21.6</v>
       </c>
     </row>
-    <row r="59" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
         <v>524</v>
       </c>
@@ -3560,7 +3560,7 @@
         <v>64.8</v>
       </c>
     </row>
-    <row r="60" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
         <v>525</v>
       </c>
@@ -3577,7 +3577,7 @@
         <v>25.8</v>
       </c>
     </row>
-    <row r="61" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
         <v>526</v>
       </c>
@@ -3594,7 +3594,7 @@
         <v>24.5</v>
       </c>
     </row>
-    <row r="62" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
         <v>527</v>
       </c>
@@ -3611,7 +3611,7 @@
         <v>42.7</v>
       </c>
     </row>
-    <row r="63" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
         <v>528</v>
       </c>
@@ -3628,7 +3628,7 @@
         <v>5.4</v>
       </c>
     </row>
-    <row r="64" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
         <v>529</v>
       </c>
@@ -3645,7 +3645,7 @@
         <v>6.9</v>
       </c>
     </row>
-    <row r="65" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
         <v>530</v>
       </c>
@@ -3662,7 +3662,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="66" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
         <v>531</v>
       </c>
@@ -3679,7 +3679,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="67" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
         <v>532</v>
       </c>
@@ -3696,7 +3696,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="68" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
         <v>533</v>
       </c>
@@ -3713,7 +3713,7 @@
         <v>244</v>
       </c>
     </row>
-    <row r="69" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
         <v>534</v>
       </c>
@@ -3730,7 +3730,7 @@
         <v>297</v>
       </c>
     </row>
-    <row r="70" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
         <v>535</v>
       </c>
@@ -3747,7 +3747,7 @@
         <v>265</v>
       </c>
     </row>
-    <row r="71" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
         <v>536</v>
       </c>
@@ -3764,7 +3764,7 @@
         <v>259</v>
       </c>
     </row>
-    <row r="72" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
         <v>537</v>
       </c>
@@ -3781,7 +3781,7 @@
         <v>273</v>
       </c>
     </row>
-    <row r="73" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
         <v>538</v>
       </c>
@@ -3798,7 +3798,7 @@
         <v>139.69999999999999</v>
       </c>
     </row>
-    <row r="74" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
         <v>539</v>
       </c>
@@ -3815,7 +3815,7 @@
         <v>152.69999999999999</v>
       </c>
     </row>
-    <row r="75" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
         <v>540</v>
       </c>
@@ -3832,7 +3832,7 @@
         <v>253</v>
       </c>
     </row>
-    <row r="76" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
         <v>541</v>
       </c>
@@ -3849,7 +3849,7 @@
         <v>686.3</v>
       </c>
     </row>
-    <row r="77" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
         <v>542</v>
       </c>
@@ -3866,7 +3866,7 @@
         <v>468.7</v>
       </c>
     </row>
-    <row r="78" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
         <v>543</v>
       </c>
@@ -3883,7 +3883,7 @@
         <v>516</v>
       </c>
     </row>
-    <row r="79" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
         <v>544</v>
       </c>
@@ -3900,7 +3900,7 @@
         <v>4.5</v>
       </c>
     </row>
-    <row r="80" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
         <v>545</v>
       </c>
@@ -3917,7 +3917,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="81" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
         <v>546</v>
       </c>
@@ -3934,7 +3934,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="82" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
         <v>547</v>
       </c>
@@ -3951,7 +3951,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="83" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
         <v>548</v>
       </c>
@@ -3968,7 +3968,7 @@
         <v>199</v>
       </c>
     </row>
-    <row r="84" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A84" t="s">
         <v>549</v>
       </c>
@@ -3985,7 +3985,7 @@
         <v>188</v>
       </c>
     </row>
-    <row r="85" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
         <v>550</v>
       </c>
@@ -4002,7 +4002,7 @@
         <v>35.5</v>
       </c>
     </row>
-    <row r="86" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A86" t="s">
         <v>551</v>
       </c>
@@ -4019,7 +4019,7 @@
         <v>17.5</v>
       </c>
     </row>
-    <row r="87" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A87" t="s">
         <v>552</v>
       </c>
@@ -4036,7 +4036,7 @@
         <v>61.9</v>
       </c>
     </row>
-    <row r="88" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A88" t="s">
         <v>553</v>
       </c>
@@ -4053,7 +4053,7 @@
         <v>48.8</v>
       </c>
     </row>
-    <row r="89" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A89" t="s">
         <v>554</v>
       </c>
@@ -4070,7 +4070,7 @@
         <v>42.6</v>
       </c>
     </row>
-    <row r="90" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A90" t="s">
         <v>555</v>
       </c>
@@ -4087,7 +4087,7 @@
         <v>38.9</v>
       </c>
     </row>
-    <row r="91" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A91" t="s">
         <v>556</v>
       </c>
@@ -4104,7 +4104,7 @@
         <v>33.799999999999997</v>
       </c>
     </row>
-    <row r="92" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A92" t="s">
         <v>557</v>
       </c>
@@ -4121,7 +4121,7 @@
         <v>30.8</v>
       </c>
     </row>
-    <row r="93" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A93" t="s">
         <v>558</v>
       </c>
@@ -4138,7 +4138,7 @@
         <v>33.5</v>
       </c>
     </row>
-    <row r="94" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A94" t="s">
         <v>559</v>
       </c>
@@ -4155,7 +4155,7 @@
         <v>70.5</v>
       </c>
     </row>
-    <row r="95" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A95" t="s">
         <v>560</v>
       </c>
@@ -4172,7 +4172,7 @@
         <v>59.3</v>
       </c>
     </row>
-    <row r="96" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A96" t="s">
         <v>561</v>
       </c>
@@ -4189,7 +4189,7 @@
         <v>67.099999999999994</v>
       </c>
     </row>
-    <row r="97" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A97" t="s">
         <v>562</v>
       </c>
@@ -4206,7 +4206,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="98" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A98" t="s">
         <v>563</v>
       </c>
@@ -4223,7 +4223,7 @@
         <v>58.4</v>
       </c>
     </row>
-    <row r="99" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A99" t="s">
         <v>564</v>
       </c>
@@ -4240,7 +4240,7 @@
         <v>32.6</v>
       </c>
     </row>
-    <row r="100" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A100" t="s">
         <v>565</v>
       </c>
@@ -4257,7 +4257,7 @@
         <v>24.6</v>
       </c>
     </row>
-    <row r="101" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A101" t="s">
         <v>566</v>
       </c>
@@ -4274,7 +4274,7 @@
         <v>35.4</v>
       </c>
     </row>
-    <row r="102" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A102" t="s">
         <v>567</v>
       </c>
@@ -4291,7 +4291,7 @@
         <v>23.1</v>
       </c>
     </row>
-    <row r="103" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A103" t="s">
         <v>568</v>
       </c>
@@ -4308,7 +4308,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="104" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A104" t="s">
         <v>569</v>
       </c>
@@ -4325,7 +4325,7 @@
         <v>20.3</v>
       </c>
     </row>
-    <row r="105" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A105" t="s">
         <v>570</v>
       </c>
@@ -4342,7 +4342,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="106" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A106" t="s">
         <v>571</v>
       </c>
@@ -4359,7 +4359,7 @@
         <v>6.8</v>
       </c>
     </row>
-    <row r="107" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A107" t="s">
         <v>572</v>
       </c>
@@ -4376,7 +4376,7 @@
         <v>5.4</v>
       </c>
     </row>
-    <row r="108" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A108" t="s">
         <v>573</v>
       </c>
@@ -4393,7 +4393,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="109" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A109" t="s">
         <v>574</v>
       </c>
@@ -4410,7 +4410,7 @@
         <v>4.0999999999999996</v>
       </c>
     </row>
-    <row r="110" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A110" t="s">
         <v>575</v>
       </c>
@@ -4427,7 +4427,7 @@
         <v>4.4000000000000004</v>
       </c>
     </row>
-    <row r="111" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A111" t="s">
         <v>576</v>
       </c>
@@ -4444,7 +4444,7 @@
         <v>246</v>
       </c>
     </row>
-    <row r="112" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A112" t="s">
         <v>577</v>
       </c>
@@ -4461,7 +4461,7 @@
         <v>168</v>
       </c>
     </row>
-    <row r="113" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A113" t="s">
         <v>578</v>
       </c>
@@ -4478,7 +4478,7 @@
         <v>5.7</v>
       </c>
     </row>
-    <row r="114" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A114" t="s">
         <v>579</v>
       </c>
@@ -4495,7 +4495,7 @@
         <v>4.5</v>
       </c>
     </row>
-    <row r="115" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A115" t="s">
         <v>580</v>
       </c>
@@ -4512,7 +4512,7 @@
         <v>7.2</v>
       </c>
     </row>
-    <row r="116" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A116" t="s">
         <v>581</v>
       </c>
@@ -4529,7 +4529,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="117" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A117" t="s">
         <v>582</v>
       </c>
@@ -4557,13 +4557,13 @@
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0B00-000000000000}">
   <dimension ref="A1:E26"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="60.875" customWidth="1"/>
     <col min="2" max="5" width="20.875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>11</v>
       </c>
@@ -4580,7 +4580,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="2" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>374</v>
       </c>
@@ -4597,7 +4597,7 @@
         <v>15.5</v>
       </c>
     </row>
-    <row r="3" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>375</v>
       </c>
@@ -4614,7 +4614,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="4" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>376</v>
       </c>
@@ -4631,7 +4631,7 @@
         <v>12.4</v>
       </c>
     </row>
-    <row r="5" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>377</v>
       </c>
@@ -4648,7 +4648,7 @@
         <v>12.4</v>
       </c>
     </row>
-    <row r="6" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>378</v>
       </c>
@@ -4665,7 +4665,7 @@
         <v>12.6</v>
       </c>
     </row>
-    <row r="7" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>379</v>
       </c>
@@ -4682,7 +4682,7 @@
         <v>12.3</v>
       </c>
     </row>
-    <row r="8" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>380</v>
       </c>
@@ -4699,7 +4699,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="9" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>381</v>
       </c>
@@ -4716,7 +4716,7 @@
         <v>12.1</v>
       </c>
     </row>
-    <row r="10" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>382</v>
       </c>
@@ -4733,7 +4733,7 @@
         <v>13.6</v>
       </c>
     </row>
-    <row r="11" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>383</v>
       </c>
@@ -4750,7 +4750,7 @@
         <v>10.3</v>
       </c>
     </row>
-    <row r="12" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>384</v>
       </c>
@@ -4767,7 +4767,7 @@
         <v>12.4</v>
       </c>
     </row>
-    <row r="13" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>385</v>
       </c>
@@ -4784,7 +4784,7 @@
         <v>8.5</v>
       </c>
     </row>
-    <row r="14" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>386</v>
       </c>
@@ -4801,7 +4801,7 @@
         <v>11.7</v>
       </c>
     </row>
-    <row r="15" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>387</v>
       </c>
@@ -4818,7 +4818,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="16" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>388</v>
       </c>
@@ -4835,7 +4835,7 @@
         <v>12.4</v>
       </c>
     </row>
-    <row r="17" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>389</v>
       </c>
@@ -4852,7 +4852,7 @@
         <v>16.3</v>
       </c>
     </row>
-    <row r="18" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>390</v>
       </c>
@@ -4869,7 +4869,7 @@
         <v>4.0999999999999996</v>
       </c>
     </row>
-    <row r="19" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>391</v>
       </c>
@@ -4886,7 +4886,7 @@
         <v>9.3000000000000007</v>
       </c>
     </row>
-    <row r="20" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>583</v>
       </c>
@@ -4897,7 +4897,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>584</v>
       </c>
@@ -4914,7 +4914,7 @@
         <v>71.3</v>
       </c>
     </row>
-    <row r="22" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>585</v>
       </c>
@@ -4931,7 +4931,7 @@
         <v>53.2</v>
       </c>
     </row>
-    <row r="23" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>586</v>
       </c>
@@ -4948,7 +4948,7 @@
         <v>47.6</v>
       </c>
     </row>
-    <row r="24" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>587</v>
       </c>
@@ -4965,7 +4965,7 @@
         <v>29.9</v>
       </c>
     </row>
-    <row r="25" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>588</v>
       </c>
@@ -4982,7 +4982,7 @@
         <v>12.4</v>
       </c>
     </row>
-    <row r="26" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>589</v>
       </c>
@@ -5010,13 +5010,13 @@
 <file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0C00-000000000000}">
   <dimension ref="A1:E49"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="60.875" customWidth="1"/>
     <col min="2" max="5" width="20.875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>11</v>
       </c>
@@ -5033,7 +5033,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="2" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>374</v>
       </c>
@@ -5050,7 +5050,7 @@
         <v>15.5</v>
       </c>
     </row>
-    <row r="3" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>375</v>
       </c>
@@ -5067,7 +5067,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="4" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>376</v>
       </c>
@@ -5084,7 +5084,7 @@
         <v>12.4</v>
       </c>
     </row>
-    <row r="5" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>377</v>
       </c>
@@ -5101,7 +5101,7 @@
         <v>12.4</v>
       </c>
     </row>
-    <row r="6" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>378</v>
       </c>
@@ -5118,7 +5118,7 @@
         <v>12.6</v>
       </c>
     </row>
-    <row r="7" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>379</v>
       </c>
@@ -5135,7 +5135,7 @@
         <v>12.3</v>
       </c>
     </row>
-    <row r="8" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>380</v>
       </c>
@@ -5152,7 +5152,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="9" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>381</v>
       </c>
@@ -5169,7 +5169,7 @@
         <v>12.1</v>
       </c>
     </row>
-    <row r="10" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>382</v>
       </c>
@@ -5186,7 +5186,7 @@
         <v>13.6</v>
       </c>
     </row>
-    <row r="11" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>383</v>
       </c>
@@ -5203,7 +5203,7 @@
         <v>10.3</v>
       </c>
     </row>
-    <row r="12" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>384</v>
       </c>
@@ -5220,7 +5220,7 @@
         <v>12.4</v>
       </c>
     </row>
-    <row r="13" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>385</v>
       </c>
@@ -5237,7 +5237,7 @@
         <v>8.5</v>
       </c>
     </row>
-    <row r="14" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>386</v>
       </c>
@@ -5254,7 +5254,7 @@
         <v>11.7</v>
       </c>
     </row>
-    <row r="15" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>387</v>
       </c>
@@ -5271,7 +5271,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="16" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>388</v>
       </c>
@@ -5288,7 +5288,7 @@
         <v>12.4</v>
       </c>
     </row>
-    <row r="17" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>389</v>
       </c>
@@ -5305,7 +5305,7 @@
         <v>16.3</v>
       </c>
     </row>
-    <row r="18" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>390</v>
       </c>
@@ -5322,7 +5322,7 @@
         <v>4.0999999999999996</v>
       </c>
     </row>
-    <row r="19" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>391</v>
       </c>
@@ -5339,7 +5339,7 @@
         <v>9.3000000000000007</v>
       </c>
     </row>
-    <row r="20" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>590</v>
       </c>
@@ -5350,7 +5350,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>591</v>
       </c>
@@ -5361,7 +5361,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>584</v>
       </c>
@@ -5378,7 +5378,7 @@
         <v>71.3</v>
       </c>
     </row>
-    <row r="23" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>592</v>
       </c>
@@ -5395,7 +5395,7 @@
         <v>62.6</v>
       </c>
     </row>
-    <row r="24" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>593</v>
       </c>
@@ -5412,7 +5412,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="25" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>585</v>
       </c>
@@ -5429,7 +5429,7 @@
         <v>53.2</v>
       </c>
     </row>
-    <row r="26" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>594</v>
       </c>
@@ -5446,7 +5446,7 @@
         <v>48.3</v>
       </c>
     </row>
-    <row r="27" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>586</v>
       </c>
@@ -5463,7 +5463,7 @@
         <v>47.6</v>
       </c>
     </row>
-    <row r="28" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
         <v>595</v>
       </c>
@@ -5480,7 +5480,7 @@
         <v>42.5</v>
       </c>
     </row>
-    <row r="29" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
         <v>596</v>
       </c>
@@ -5497,7 +5497,7 @@
         <v>35.4</v>
       </c>
     </row>
-    <row r="30" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
         <v>597</v>
       </c>
@@ -5514,7 +5514,7 @@
         <v>23.4</v>
       </c>
     </row>
-    <row r="31" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
         <v>598</v>
       </c>
@@ -5531,7 +5531,7 @@
         <v>16.8</v>
       </c>
     </row>
-    <row r="32" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
         <v>599</v>
       </c>
@@ -5548,7 +5548,7 @@
         <v>24.1</v>
       </c>
     </row>
-    <row r="33" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
         <v>600</v>
       </c>
@@ -5565,7 +5565,7 @@
         <v>15.2</v>
       </c>
     </row>
-    <row r="34" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
         <v>601</v>
       </c>
@@ -5582,7 +5582,7 @@
         <v>20.399999999999999</v>
       </c>
     </row>
-    <row r="35" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
         <v>602</v>
       </c>
@@ -5599,7 +5599,7 @@
         <v>24.4</v>
       </c>
     </row>
-    <row r="36" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
         <v>603</v>
       </c>
@@ -5616,7 +5616,7 @@
         <v>23.3</v>
       </c>
     </row>
-    <row r="37" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
         <v>604</v>
       </c>
@@ -5633,7 +5633,7 @@
         <v>52.5</v>
       </c>
     </row>
-    <row r="38" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
         <v>605</v>
       </c>
@@ -5650,7 +5650,7 @@
         <v>48.3</v>
       </c>
     </row>
-    <row r="39" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
         <v>606</v>
       </c>
@@ -5667,7 +5667,7 @@
         <v>68.2</v>
       </c>
     </row>
-    <row r="40" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
         <v>607</v>
       </c>
@@ -5684,7 +5684,7 @@
         <v>48.6</v>
       </c>
     </row>
-    <row r="41" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
         <v>608</v>
       </c>
@@ -5701,7 +5701,7 @@
         <v>28.8</v>
       </c>
     </row>
-    <row r="42" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
         <v>609</v>
       </c>
@@ -5718,7 +5718,7 @@
         <v>50.8</v>
       </c>
     </row>
-    <row r="43" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
         <v>610</v>
       </c>
@@ -5735,7 +5735,7 @@
         <v>41.8</v>
       </c>
     </row>
-    <row r="44" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
         <v>611</v>
       </c>
@@ -5752,7 +5752,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="45" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
         <v>612</v>
       </c>
@@ -5769,7 +5769,7 @@
         <v>68.2</v>
       </c>
     </row>
-    <row r="46" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
         <v>613</v>
       </c>
@@ -5786,7 +5786,7 @@
         <v>56.7</v>
       </c>
     </row>
-    <row r="47" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
         <v>614</v>
       </c>
@@ -5803,7 +5803,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="48" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
         <v>587</v>
       </c>
@@ -5820,7 +5820,7 @@
         <v>29.9</v>
       </c>
     </row>
-    <row r="49" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
         <v>589</v>
       </c>
@@ -5848,13 +5848,13 @@
 <file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0D00-000000000000}">
   <dimension ref="A1:E21"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="60.875" customWidth="1"/>
     <col min="2" max="5" width="20.875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>11</v>
       </c>
@@ -5871,7 +5871,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="2" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>374</v>
       </c>
@@ -5888,7 +5888,7 @@
         <v>15.5</v>
       </c>
     </row>
-    <row r="3" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>375</v>
       </c>
@@ -5905,7 +5905,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="4" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>376</v>
       </c>
@@ -5922,7 +5922,7 @@
         <v>12.4</v>
       </c>
     </row>
-    <row r="5" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>377</v>
       </c>
@@ -5939,7 +5939,7 @@
         <v>12.4</v>
       </c>
     </row>
-    <row r="6" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>378</v>
       </c>
@@ -5956,7 +5956,7 @@
         <v>12.6</v>
       </c>
     </row>
-    <row r="7" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>379</v>
       </c>
@@ -5973,7 +5973,7 @@
         <v>12.3</v>
       </c>
     </row>
-    <row r="8" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>380</v>
       </c>
@@ -5990,7 +5990,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="9" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>381</v>
       </c>
@@ -6007,7 +6007,7 @@
         <v>12.1</v>
       </c>
     </row>
-    <row r="10" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>382</v>
       </c>
@@ -6024,7 +6024,7 @@
         <v>13.6</v>
       </c>
     </row>
-    <row r="11" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>383</v>
       </c>
@@ -6041,7 +6041,7 @@
         <v>10.3</v>
       </c>
     </row>
-    <row r="12" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>384</v>
       </c>
@@ -6058,7 +6058,7 @@
         <v>12.4</v>
       </c>
     </row>
-    <row r="13" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>385</v>
       </c>
@@ -6075,7 +6075,7 @@
         <v>8.5</v>
       </c>
     </row>
-    <row r="14" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>386</v>
       </c>
@@ -6092,7 +6092,7 @@
         <v>11.7</v>
       </c>
     </row>
-    <row r="15" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>387</v>
       </c>
@@ -6109,7 +6109,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="16" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>388</v>
       </c>
@@ -6126,7 +6126,7 @@
         <v>12.4</v>
       </c>
     </row>
-    <row r="17" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>389</v>
       </c>
@@ -6143,7 +6143,7 @@
         <v>16.3</v>
       </c>
     </row>
-    <row r="18" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>390</v>
       </c>
@@ -6160,7 +6160,7 @@
         <v>4.0999999999999996</v>
       </c>
     </row>
-    <row r="19" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>391</v>
       </c>
@@ -6177,7 +6177,7 @@
         <v>9.3000000000000007</v>
       </c>
     </row>
-    <row r="20" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>615</v>
       </c>
@@ -6188,7 +6188,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>588</v>
       </c>
@@ -6216,13 +6216,13 @@
 <file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0E00-000000000000}">
   <dimension ref="A1:E4"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="60.875" customWidth="1"/>
     <col min="2" max="5" width="20.875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>11</v>
       </c>
@@ -6239,7 +6239,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="2" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>616</v>
       </c>
@@ -6256,7 +6256,7 @@
         <v>2.9</v>
       </c>
     </row>
-    <row r="3" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>617</v>
       </c>
@@ -6267,7 +6267,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>588</v>
       </c>
@@ -6295,13 +6295,13 @@
 <file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0F00-000000000000}">
   <dimension ref="A1:E52"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="60.875" customWidth="1"/>
     <col min="2" max="5" width="20.875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>11</v>
       </c>
@@ -6318,7 +6318,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="2" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>374</v>
       </c>
@@ -6335,7 +6335,7 @@
         <v>15.5</v>
       </c>
     </row>
-    <row r="3" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>375</v>
       </c>
@@ -6352,7 +6352,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="4" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>376</v>
       </c>
@@ -6369,7 +6369,7 @@
         <v>12.4</v>
       </c>
     </row>
-    <row r="5" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>377</v>
       </c>
@@ -6386,7 +6386,7 @@
         <v>12.4</v>
       </c>
     </row>
-    <row r="6" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>378</v>
       </c>
@@ -6403,7 +6403,7 @@
         <v>12.6</v>
       </c>
     </row>
-    <row r="7" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>379</v>
       </c>
@@ -6420,7 +6420,7 @@
         <v>12.3</v>
       </c>
     </row>
-    <row r="8" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>380</v>
       </c>
@@ -6437,7 +6437,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="9" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>381</v>
       </c>
@@ -6454,7 +6454,7 @@
         <v>12.1</v>
       </c>
     </row>
-    <row r="10" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>382</v>
       </c>
@@ -6471,7 +6471,7 @@
         <v>13.6</v>
       </c>
     </row>
-    <row r="11" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>383</v>
       </c>
@@ -6488,7 +6488,7 @@
         <v>10.3</v>
       </c>
     </row>
-    <row r="12" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>384</v>
       </c>
@@ -6505,7 +6505,7 @@
         <v>12.4</v>
       </c>
     </row>
-    <row r="13" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>385</v>
       </c>
@@ -6522,7 +6522,7 @@
         <v>8.5</v>
       </c>
     </row>
-    <row r="14" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>386</v>
       </c>
@@ -6539,7 +6539,7 @@
         <v>11.7</v>
       </c>
     </row>
-    <row r="15" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>387</v>
       </c>
@@ -6556,7 +6556,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="16" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>388</v>
       </c>
@@ -6573,7 +6573,7 @@
         <v>12.4</v>
       </c>
     </row>
-    <row r="17" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>389</v>
       </c>
@@ -6590,7 +6590,7 @@
         <v>16.3</v>
       </c>
     </row>
-    <row r="18" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>390</v>
       </c>
@@ -6607,7 +6607,7 @@
         <v>4.0999999999999996</v>
       </c>
     </row>
-    <row r="19" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>391</v>
       </c>
@@ -6624,7 +6624,7 @@
         <v>9.3000000000000007</v>
       </c>
     </row>
-    <row r="20" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>361</v>
       </c>
@@ -6641,7 +6641,7 @@
         <v>17.8</v>
       </c>
     </row>
-    <row r="21" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>362</v>
       </c>
@@ -6658,7 +6658,7 @@
         <v>12.9</v>
       </c>
     </row>
-    <row r="22" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>363</v>
       </c>
@@ -6675,7 +6675,7 @@
         <v>15.7</v>
       </c>
     </row>
-    <row r="23" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>364</v>
       </c>
@@ -6692,7 +6692,7 @@
         <v>9.6</v>
       </c>
     </row>
-    <row r="24" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>365</v>
       </c>
@@ -6709,7 +6709,7 @@
         <v>6.1</v>
       </c>
     </row>
-    <row r="25" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>366</v>
       </c>
@@ -6726,7 +6726,7 @@
         <v>6.9</v>
       </c>
     </row>
-    <row r="26" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>367</v>
       </c>
@@ -6743,7 +6743,7 @@
         <v>7.7</v>
       </c>
     </row>
-    <row r="27" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>368</v>
       </c>
@@ -6760,7 +6760,7 @@
         <v>6.7</v>
       </c>
     </row>
-    <row r="28" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
         <v>369</v>
       </c>
@@ -6777,7 +6777,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="29" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
         <v>370</v>
       </c>
@@ -6794,7 +6794,7 @@
         <v>7.9</v>
       </c>
     </row>
-    <row r="30" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
         <v>371</v>
       </c>
@@ -6811,7 +6811,7 @@
         <v>6.9</v>
       </c>
     </row>
-    <row r="31" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
         <v>372</v>
       </c>
@@ -6828,7 +6828,7 @@
         <v>7.1</v>
       </c>
     </row>
-    <row r="32" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
         <v>373</v>
       </c>
@@ -6845,7 +6845,7 @@
         <v>10.3</v>
       </c>
     </row>
-    <row r="33" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
         <v>374</v>
       </c>
@@ -6862,7 +6862,7 @@
         <v>15.5</v>
       </c>
     </row>
-    <row r="34" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
         <v>375</v>
       </c>
@@ -6879,7 +6879,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="35" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
         <v>376</v>
       </c>
@@ -6896,7 +6896,7 @@
         <v>12.4</v>
       </c>
     </row>
-    <row r="36" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
         <v>377</v>
       </c>
@@ -6913,7 +6913,7 @@
         <v>12.4</v>
       </c>
     </row>
-    <row r="37" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
         <v>378</v>
       </c>
@@ -6930,7 +6930,7 @@
         <v>12.6</v>
       </c>
     </row>
-    <row r="38" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
         <v>379</v>
       </c>
@@ -6947,7 +6947,7 @@
         <v>12.3</v>
       </c>
     </row>
-    <row r="39" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
         <v>380</v>
       </c>
@@ -6964,7 +6964,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="40" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
         <v>381</v>
       </c>
@@ -6981,7 +6981,7 @@
         <v>12.1</v>
       </c>
     </row>
-    <row r="41" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
         <v>382</v>
       </c>
@@ -6998,7 +6998,7 @@
         <v>13.6</v>
       </c>
     </row>
-    <row r="42" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
         <v>383</v>
       </c>
@@ -7015,7 +7015,7 @@
         <v>10.3</v>
       </c>
     </row>
-    <row r="43" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
         <v>384</v>
       </c>
@@ -7032,7 +7032,7 @@
         <v>12.4</v>
       </c>
     </row>
-    <row r="44" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
         <v>385</v>
       </c>
@@ -7049,7 +7049,7 @@
         <v>8.5</v>
       </c>
     </row>
-    <row r="45" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
         <v>386</v>
       </c>
@@ -7066,7 +7066,7 @@
         <v>11.7</v>
       </c>
     </row>
-    <row r="46" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
         <v>387</v>
       </c>
@@ -7083,7 +7083,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="47" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
         <v>388</v>
       </c>
@@ -7100,7 +7100,7 @@
         <v>12.4</v>
       </c>
     </row>
-    <row r="48" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
         <v>389</v>
       </c>
@@ -7117,7 +7117,7 @@
         <v>16.3</v>
       </c>
     </row>
-    <row r="49" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
         <v>390</v>
       </c>
@@ -7134,7 +7134,7 @@
         <v>4.0999999999999996</v>
       </c>
     </row>
-    <row r="50" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
         <v>391</v>
       </c>
@@ -7151,7 +7151,7 @@
         <v>9.3000000000000007</v>
       </c>
     </row>
-    <row r="51" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
         <v>618</v>
       </c>
@@ -7162,7 +7162,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="52" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
         <v>588</v>
       </c>
@@ -7190,13 +7190,13 @@
 <file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1000-000000000000}">
   <dimension ref="A1:E51"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="60.875" customWidth="1"/>
     <col min="2" max="5" width="20.875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>11</v>
       </c>
@@ -7213,7 +7213,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="2" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>619</v>
       </c>
@@ -7230,7 +7230,7 @@
         <v>5.0000000000000009</v>
       </c>
     </row>
-    <row r="3" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>620</v>
       </c>
@@ -7247,7 +7247,7 @@
         <v>6.27</v>
       </c>
     </row>
-    <row r="4" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>621</v>
       </c>
@@ -7264,7 +7264,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>622</v>
       </c>
@@ -7281,7 +7281,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>623</v>
       </c>
@@ -7298,7 +7298,7 @@
         <v>23.2</v>
       </c>
     </row>
-    <row r="7" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>624</v>
       </c>
@@ -7315,7 +7315,7 @@
         <v>16.7</v>
       </c>
     </row>
-    <row r="8" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>625</v>
       </c>
@@ -7332,7 +7332,7 @@
         <v>23.9</v>
       </c>
     </row>
-    <row r="9" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>626</v>
       </c>
@@ -7349,7 +7349,7 @@
         <v>14.9</v>
       </c>
     </row>
-    <row r="10" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>627</v>
       </c>
@@ -7366,7 +7366,7 @@
         <v>19.899999999999999</v>
       </c>
     </row>
-    <row r="11" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>628</v>
       </c>
@@ -7383,7 +7383,7 @@
         <v>23.7</v>
       </c>
     </row>
-    <row r="12" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>629</v>
       </c>
@@ -7400,7 +7400,7 @@
         <v>22.9</v>
       </c>
     </row>
-    <row r="13" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>630</v>
       </c>
@@ -7417,7 +7417,7 @@
         <v>22.2</v>
       </c>
     </row>
-    <row r="14" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>631</v>
       </c>
@@ -7434,7 +7434,7 @@
         <v>26.1</v>
       </c>
     </row>
-    <row r="15" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>632</v>
       </c>
@@ -7451,7 +7451,7 @@
         <v>30.1</v>
       </c>
     </row>
-    <row r="16" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>633</v>
       </c>
@@ -7468,7 +7468,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="17" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>634</v>
       </c>
@@ -7485,7 +7485,7 @@
         <v>20.5</v>
       </c>
     </row>
-    <row r="18" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>635</v>
       </c>
@@ -7502,7 +7502,7 @@
         <v>28.3</v>
       </c>
     </row>
-    <row r="19" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>636</v>
       </c>
@@ -7519,7 +7519,7 @@
         <v>22.9</v>
       </c>
     </row>
-    <row r="20" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>637</v>
       </c>
@@ -7536,7 +7536,7 @@
         <v>23.3</v>
       </c>
     </row>
-    <row r="21" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>638</v>
       </c>
@@ -7553,7 +7553,7 @@
         <v>23.1</v>
       </c>
     </row>
-    <row r="22" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>639</v>
       </c>
@@ -7570,7 +7570,7 @@
         <v>50.1</v>
       </c>
     </row>
-    <row r="23" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>640</v>
       </c>
@@ -7587,7 +7587,7 @@
         <v>46.9</v>
       </c>
     </row>
-    <row r="24" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>641</v>
       </c>
@@ -7604,7 +7604,7 @@
         <v>65.7</v>
       </c>
     </row>
-    <row r="25" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>642</v>
       </c>
@@ -7621,7 +7621,7 @@
         <v>46.5</v>
       </c>
     </row>
-    <row r="26" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>643</v>
       </c>
@@ -7638,7 +7638,7 @@
         <v>43.7</v>
       </c>
     </row>
-    <row r="27" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>644</v>
       </c>
@@ -7655,7 +7655,7 @@
         <v>41.5</v>
       </c>
     </row>
-    <row r="28" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
         <v>645</v>
       </c>
@@ -7672,7 +7672,7 @@
         <v>38.6</v>
       </c>
     </row>
-    <row r="29" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
         <v>646</v>
       </c>
@@ -7689,7 +7689,7 @@
         <v>30.5</v>
       </c>
     </row>
-    <row r="30" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
         <v>647</v>
       </c>
@@ -7706,7 +7706,7 @@
         <v>25.9</v>
       </c>
     </row>
-    <row r="31" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
         <v>648</v>
       </c>
@@ -7723,7 +7723,7 @@
         <v>55.1</v>
       </c>
     </row>
-    <row r="32" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
         <v>649</v>
       </c>
@@ -7740,7 +7740,7 @@
         <v>40.700000000000003</v>
       </c>
     </row>
-    <row r="33" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
         <v>650</v>
       </c>
@@ -7757,7 +7757,7 @@
         <v>37.700000000000003</v>
       </c>
     </row>
-    <row r="34" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
         <v>651</v>
       </c>
@@ -7774,7 +7774,7 @@
         <v>27.4</v>
       </c>
     </row>
-    <row r="35" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
         <v>652</v>
       </c>
@@ -7791,7 +7791,7 @@
         <v>46.7</v>
       </c>
     </row>
-    <row r="36" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
         <v>653</v>
       </c>
@@ -7808,7 +7808,7 @@
         <v>27.4</v>
       </c>
     </row>
-    <row r="37" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
         <v>654</v>
       </c>
@@ -7825,7 +7825,7 @@
         <v>48.8</v>
       </c>
     </row>
-    <row r="38" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
         <v>655</v>
       </c>
@@ -7842,7 +7842,7 @@
         <v>40.799999999999997</v>
       </c>
     </row>
-    <row r="39" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
         <v>656</v>
       </c>
@@ -7859,7 +7859,7 @@
         <v>33.4</v>
       </c>
     </row>
-    <row r="40" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
         <v>657</v>
       </c>
@@ -7876,7 +7876,7 @@
         <v>58.7</v>
       </c>
     </row>
-    <row r="41" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
         <v>658</v>
       </c>
@@ -7893,7 +7893,7 @@
         <v>55.8</v>
       </c>
     </row>
-    <row r="42" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
         <v>659</v>
       </c>
@@ -7910,7 +7910,7 @@
         <v>47.3</v>
       </c>
     </row>
-    <row r="43" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
         <v>660</v>
       </c>
@@ -7927,7 +7927,7 @@
         <v>73.3</v>
       </c>
     </row>
-    <row r="44" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
         <v>661</v>
       </c>
@@ -7944,7 +7944,7 @@
         <v>48.7</v>
       </c>
     </row>
-    <row r="45" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
         <v>662</v>
       </c>
@@ -7961,7 +7961,7 @@
         <v>51.9</v>
       </c>
     </row>
-    <row r="46" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
         <v>663</v>
       </c>
@@ -7978,7 +7978,7 @@
         <v>47.9</v>
       </c>
     </row>
-    <row r="47" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
         <v>664</v>
       </c>
@@ -7995,7 +7995,7 @@
         <v>32.5</v>
       </c>
     </row>
-    <row r="48" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
         <v>665</v>
       </c>
@@ -8012,7 +8012,7 @@
         <v>29.3</v>
       </c>
     </row>
-    <row r="49" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
         <v>666</v>
       </c>
@@ -8029,7 +8029,7 @@
         <v>59.4</v>
       </c>
     </row>
-    <row r="50" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
         <v>667</v>
       </c>
@@ -8046,7 +8046,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="51" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
         <v>668</v>
       </c>
@@ -8074,13 +8074,13 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:E85"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="60.875" customWidth="1"/>
     <col min="2" max="5" width="20.875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>11</v>
       </c>
@@ -8097,7 +8097,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="2" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>16</v>
       </c>
@@ -8114,7 +8114,7 @@
         <v>37.1</v>
       </c>
     </row>
-    <row r="3" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>17</v>
       </c>
@@ -8131,7 +8131,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="4" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>18</v>
       </c>
@@ -8148,7 +8148,7 @@
         <v>38.200000000000003</v>
       </c>
     </row>
-    <row r="5" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>19</v>
       </c>
@@ -8165,7 +8165,7 @@
         <v>37.4</v>
       </c>
     </row>
-    <row r="6" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>20</v>
       </c>
@@ -8182,7 +8182,7 @@
         <v>50.1</v>
       </c>
     </row>
-    <row r="7" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>21</v>
       </c>
@@ -8199,7 +8199,7 @@
         <v>41.2</v>
       </c>
     </row>
-    <row r="8" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>22</v>
       </c>
@@ -8216,7 +8216,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="9" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>23</v>
       </c>
@@ -8233,7 +8233,7 @@
         <v>63.6</v>
       </c>
     </row>
-    <row r="10" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>24</v>
       </c>
@@ -8250,7 +8250,7 @@
         <v>55.9</v>
       </c>
     </row>
-    <row r="11" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>25</v>
       </c>
@@ -8267,7 +8267,7 @@
         <v>54.9</v>
       </c>
     </row>
-    <row r="12" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>26</v>
       </c>
@@ -8284,7 +8284,7 @@
         <v>45.6</v>
       </c>
     </row>
-    <row r="13" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>27</v>
       </c>
@@ -8301,7 +8301,7 @@
         <v>74.099999999999994</v>
       </c>
     </row>
-    <row r="14" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>28</v>
       </c>
@@ -8318,7 +8318,7 @@
         <v>50.6</v>
       </c>
     </row>
-    <row r="15" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>29</v>
       </c>
@@ -8335,7 +8335,7 @@
         <v>41.5</v>
       </c>
     </row>
-    <row r="16" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>30</v>
       </c>
@@ -8352,7 +8352,7 @@
         <v>37.799999999999997</v>
       </c>
     </row>
-    <row r="17" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>20</v>
       </c>
@@ -8369,7 +8369,7 @@
         <v>55.8</v>
       </c>
     </row>
-    <row r="18" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>21</v>
       </c>
@@ -8386,7 +8386,7 @@
         <v>49.4</v>
       </c>
     </row>
-    <row r="19" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>22</v>
       </c>
@@ -8403,7 +8403,7 @@
         <v>47.5</v>
       </c>
     </row>
-    <row r="20" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>31</v>
       </c>
@@ -8420,7 +8420,7 @@
         <v>54.1</v>
       </c>
     </row>
-    <row r="21" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>32</v>
       </c>
@@ -8437,7 +8437,7 @@
         <v>65.7</v>
       </c>
     </row>
-    <row r="22" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>33</v>
       </c>
@@ -8454,7 +8454,7 @@
         <v>56.4</v>
       </c>
     </row>
-    <row r="23" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>34</v>
       </c>
@@ -8471,7 +8471,7 @@
         <v>52.8</v>
       </c>
     </row>
-    <row r="24" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>35</v>
       </c>
@@ -8488,7 +8488,7 @@
         <v>56.5</v>
       </c>
     </row>
-    <row r="25" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>36</v>
       </c>
@@ -8505,7 +8505,7 @@
         <v>60.8</v>
       </c>
     </row>
-    <row r="26" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>37</v>
       </c>
@@ -8522,7 +8522,7 @@
         <v>56.1</v>
       </c>
     </row>
-    <row r="27" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>38</v>
       </c>
@@ -8539,7 +8539,7 @@
         <v>58.3</v>
       </c>
     </row>
-    <row r="28" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
         <v>39</v>
       </c>
@@ -8556,7 +8556,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="29" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
         <v>40</v>
       </c>
@@ -8573,7 +8573,7 @@
         <v>46.2</v>
       </c>
     </row>
-    <row r="30" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
         <v>41</v>
       </c>
@@ -8590,7 +8590,7 @@
         <v>55.7</v>
       </c>
     </row>
-    <row r="31" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
         <v>42</v>
       </c>
@@ -8607,7 +8607,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="32" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
         <v>43</v>
       </c>
@@ -8624,7 +8624,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="33" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
         <v>44</v>
       </c>
@@ -8641,7 +8641,7 @@
         <v>59.3</v>
       </c>
     </row>
-    <row r="34" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
         <v>45</v>
       </c>
@@ -8658,7 +8658,7 @@
         <v>40.5</v>
       </c>
     </row>
-    <row r="35" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
         <v>46</v>
       </c>
@@ -8675,7 +8675,7 @@
         <v>44.4</v>
       </c>
     </row>
-    <row r="36" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
         <v>47</v>
       </c>
@@ -8692,7 +8692,7 @@
         <v>55.6</v>
       </c>
     </row>
-    <row r="37" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
         <v>48</v>
       </c>
@@ -8709,7 +8709,7 @@
         <v>50.8</v>
       </c>
     </row>
-    <row r="38" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
         <v>49</v>
       </c>
@@ -8726,7 +8726,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="39" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
         <v>50</v>
       </c>
@@ -8743,7 +8743,7 @@
         <v>50.1</v>
       </c>
     </row>
-    <row r="40" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
         <v>51</v>
       </c>
@@ -8760,7 +8760,7 @@
         <v>60.2</v>
       </c>
     </row>
-    <row r="41" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
         <v>52</v>
       </c>
@@ -8777,7 +8777,7 @@
         <v>58.7</v>
       </c>
     </row>
-    <row r="42" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
         <v>53</v>
       </c>
@@ -8794,7 +8794,7 @@
         <v>58.4</v>
       </c>
     </row>
-    <row r="43" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
         <v>54</v>
       </c>
@@ -8811,7 +8811,7 @@
         <v>44.8</v>
       </c>
     </row>
-    <row r="44" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
         <v>55</v>
       </c>
@@ -8828,7 +8828,7 @@
         <v>46.5</v>
       </c>
     </row>
-    <row r="45" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
         <v>56</v>
       </c>
@@ -8845,7 +8845,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="46" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
         <v>57</v>
       </c>
@@ -8862,7 +8862,7 @@
         <v>54.7</v>
       </c>
     </row>
-    <row r="47" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
         <v>58</v>
       </c>
@@ -8879,7 +8879,7 @@
         <v>68.400000000000006</v>
       </c>
     </row>
-    <row r="48" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
         <v>59</v>
       </c>
@@ -8896,7 +8896,7 @@
         <v>62.6</v>
       </c>
     </row>
-    <row r="49" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
         <v>60</v>
       </c>
@@ -8913,7 +8913,7 @@
         <v>88.9</v>
       </c>
     </row>
-    <row r="50" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
         <v>61</v>
       </c>
@@ -8930,7 +8930,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="51" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
         <v>62</v>
       </c>
@@ -8947,7 +8947,7 @@
         <v>82.3</v>
       </c>
     </row>
-    <row r="52" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
         <v>63</v>
       </c>
@@ -8964,7 +8964,7 @@
         <v>83.9</v>
       </c>
     </row>
-    <row r="53" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
         <v>64</v>
       </c>
@@ -8981,7 +8981,7 @@
         <v>77.599999999999994</v>
       </c>
     </row>
-    <row r="54" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
         <v>65</v>
       </c>
@@ -8998,7 +8998,7 @@
         <v>96.4</v>
       </c>
     </row>
-    <row r="55" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
         <v>66</v>
       </c>
@@ -9015,7 +9015,7 @@
         <v>64.400000000000006</v>
       </c>
     </row>
-    <row r="56" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
         <v>67</v>
       </c>
@@ -9032,7 +9032,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="57" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
         <v>68</v>
       </c>
@@ -9049,7 +9049,7 @@
         <v>48.8</v>
       </c>
     </row>
-    <row r="58" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
         <v>69</v>
       </c>
@@ -9066,7 +9066,7 @@
         <v>73.099999999999994</v>
       </c>
     </row>
-    <row r="59" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
         <v>70</v>
       </c>
@@ -9083,7 +9083,7 @@
         <v>61.7</v>
       </c>
     </row>
-    <row r="60" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
         <v>71</v>
       </c>
@@ -9100,7 +9100,7 @@
         <v>52.8</v>
       </c>
     </row>
-    <row r="61" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
         <v>72</v>
       </c>
@@ -9117,7 +9117,7 @@
         <v>23.2</v>
       </c>
     </row>
-    <row r="62" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
         <v>73</v>
       </c>
@@ -9134,7 +9134,7 @@
         <v>79.900000000000006</v>
       </c>
     </row>
-    <row r="63" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
         <v>74</v>
       </c>
@@ -9151,7 +9151,7 @@
         <v>39.200000000000003</v>
       </c>
     </row>
-    <row r="64" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
         <v>75</v>
       </c>
@@ -9168,7 +9168,7 @@
         <v>38.4</v>
       </c>
     </row>
-    <row r="65" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
         <v>76</v>
       </c>
@@ -9185,7 +9185,7 @@
         <v>51.4</v>
       </c>
     </row>
-    <row r="66" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
         <v>77</v>
       </c>
@@ -9202,7 +9202,7 @@
         <v>41.7</v>
       </c>
     </row>
-    <row r="67" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
         <v>78</v>
       </c>
@@ -9219,7 +9219,7 @@
         <v>39.6</v>
       </c>
     </row>
-    <row r="68" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
         <v>79</v>
       </c>
@@ -9236,7 +9236,7 @@
         <v>66.099999999999994</v>
       </c>
     </row>
-    <row r="69" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
         <v>80</v>
       </c>
@@ -9253,7 +9253,7 @@
         <v>57.6</v>
       </c>
     </row>
-    <row r="70" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
         <v>81</v>
       </c>
@@ -9270,7 +9270,7 @@
         <v>55.8</v>
       </c>
     </row>
-    <row r="71" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
         <v>82</v>
       </c>
@@ -9287,7 +9287,7 @@
         <v>47.2</v>
       </c>
     </row>
-    <row r="72" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
         <v>83</v>
       </c>
@@ -9304,7 +9304,7 @@
         <v>57.3</v>
       </c>
     </row>
-    <row r="73" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
         <v>84</v>
       </c>
@@ -9321,7 +9321,7 @@
         <v>43.6</v>
       </c>
     </row>
-    <row r="74" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
         <v>85</v>
       </c>
@@ -9338,7 +9338,7 @@
         <v>52.8</v>
       </c>
     </row>
-    <row r="75" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
         <v>86</v>
       </c>
@@ -9355,7 +9355,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="76" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
         <v>87</v>
       </c>
@@ -9372,7 +9372,7 @@
         <v>61.6</v>
       </c>
     </row>
-    <row r="77" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
         <v>88</v>
       </c>
@@ -9389,7 +9389,7 @@
         <v>59.5</v>
       </c>
     </row>
-    <row r="78" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
         <v>89</v>
       </c>
@@ -9406,7 +9406,7 @@
         <v>59.4</v>
       </c>
     </row>
-    <row r="79" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
         <v>90</v>
       </c>
@@ -9423,7 +9423,7 @@
         <v>45.4</v>
       </c>
     </row>
-    <row r="80" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
         <v>91</v>
       </c>
@@ -9440,7 +9440,7 @@
         <v>47.2</v>
       </c>
     </row>
-    <row r="81" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
         <v>92</v>
       </c>
@@ -9457,7 +9457,7 @@
         <v>121.3</v>
       </c>
     </row>
-    <row r="82" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
         <v>93</v>
       </c>
@@ -9474,7 +9474,7 @@
         <v>104</v>
       </c>
     </row>
-    <row r="83" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
         <v>94</v>
       </c>
@@ -9491,7 +9491,7 @@
         <v>131</v>
       </c>
     </row>
-    <row r="84" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A84" t="s">
         <v>95</v>
       </c>
@@ -9508,7 +9508,7 @@
         <v>162.30000000000001</v>
       </c>
     </row>
-    <row r="85" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
         <v>96</v>
       </c>
@@ -9536,13 +9536,13 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:H24"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="60.875" customWidth="1"/>
     <col min="2" max="8" width="20.875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>97</v>
       </c>
@@ -9568,7 +9568,7 @@
         <v>104</v>
       </c>
     </row>
-    <row r="2" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>105</v>
       </c>
@@ -9587,8 +9587,11 @@
       <c r="F2">
         <v>100.8</v>
       </c>
-    </row>
-    <row r="3" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="H2">
+        <v>123456789</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>106</v>
       </c>
@@ -9608,7 +9611,7 @@
         <v>114.75</v>
       </c>
     </row>
-    <row r="4" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>107</v>
       </c>
@@ -9628,7 +9631,7 @@
         <v>101.25</v>
       </c>
     </row>
-    <row r="5" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>108</v>
       </c>
@@ -9648,7 +9651,7 @@
         <v>101.25</v>
       </c>
     </row>
-    <row r="6" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>109</v>
       </c>
@@ -9668,7 +9671,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="7" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>110</v>
       </c>
@@ -9688,7 +9691,7 @@
         <v>94.5</v>
       </c>
     </row>
-    <row r="8" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>111</v>
       </c>
@@ -9708,7 +9711,7 @@
         <v>68.25</v>
       </c>
     </row>
-    <row r="9" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>112</v>
       </c>
@@ -9728,7 +9731,7 @@
         <v>67.5</v>
       </c>
     </row>
-    <row r="10" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>113</v>
       </c>
@@ -9748,7 +9751,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="11" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>114</v>
       </c>
@@ -9768,7 +9771,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="12" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>115</v>
       </c>
@@ -9788,7 +9791,7 @@
         <v>225</v>
       </c>
     </row>
-    <row r="13" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>116</v>
       </c>
@@ -9808,7 +9811,7 @@
         <v>237.5</v>
       </c>
     </row>
-    <row r="14" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>117</v>
       </c>
@@ -9828,7 +9831,7 @@
         <v>231</v>
       </c>
     </row>
-    <row r="15" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>118</v>
       </c>
@@ -9848,7 +9851,7 @@
         <v>262.5</v>
       </c>
     </row>
-    <row r="16" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>119</v>
       </c>
@@ -9868,7 +9871,7 @@
         <v>341.67</v>
       </c>
     </row>
-    <row r="17" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>120</v>
       </c>
@@ -9888,7 +9891,7 @@
         <v>364.5</v>
       </c>
     </row>
-    <row r="18" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>121</v>
       </c>
@@ -9908,7 +9911,7 @@
         <v>188</v>
       </c>
     </row>
-    <row r="19" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>122</v>
       </c>
@@ -9928,7 +9931,7 @@
         <v>82.47</v>
       </c>
     </row>
-    <row r="20" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>123</v>
       </c>
@@ -9948,7 +9951,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="21" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>124</v>
       </c>
@@ -9968,7 +9971,7 @@
         <v>159.38</v>
       </c>
     </row>
-    <row r="22" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>125</v>
       </c>
@@ -9988,7 +9991,7 @@
         <v>43.75</v>
       </c>
     </row>
-    <row r="23" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>126</v>
       </c>
@@ -10008,7 +10011,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="24" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>127</v>
       </c>
@@ -10031,7 +10034,7 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
-    <ignoredError sqref="A1:H24" numberStoredAsText="1"/>
+    <ignoredError sqref="A1:H1 A3:H24 A2:G2" numberStoredAsText="1"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -10039,13 +10042,13 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:E46"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="60.875" customWidth="1"/>
     <col min="2" max="5" width="20.875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>128</v>
       </c>
@@ -10062,7 +10065,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="2" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>131</v>
       </c>
@@ -10079,7 +10082,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="3" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>132</v>
       </c>
@@ -10096,7 +10099,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="4" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>133</v>
       </c>
@@ -10113,7 +10116,7 @@
         <v>12.5</v>
       </c>
     </row>
-    <row r="5" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>134</v>
       </c>
@@ -10130,7 +10133,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="6" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>135</v>
       </c>
@@ -10147,7 +10150,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="7" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>136</v>
       </c>
@@ -10164,7 +10167,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="8" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>137</v>
       </c>
@@ -10181,7 +10184,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="9" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>138</v>
       </c>
@@ -10198,7 +10201,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="10" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>139</v>
       </c>
@@ -10215,7 +10218,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="11" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>140</v>
       </c>
@@ -10232,7 +10235,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="12" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>141</v>
       </c>
@@ -10249,7 +10252,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="13" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>142</v>
       </c>
@@ -10266,7 +10269,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="14" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>109</v>
       </c>
@@ -10283,7 +10286,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="15" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>143</v>
       </c>
@@ -10300,7 +10303,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="16" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>144</v>
       </c>
@@ -10317,7 +10320,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="17" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>145</v>
       </c>
@@ -10334,7 +10337,7 @@
         <v>67.5</v>
       </c>
     </row>
-    <row r="18" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>146</v>
       </c>
@@ -10351,7 +10354,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="19" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>147</v>
       </c>
@@ -10368,7 +10371,7 @@
         <v>62.5</v>
       </c>
     </row>
-    <row r="20" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>148</v>
       </c>
@@ -10385,7 +10388,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="21" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>149</v>
       </c>
@@ -10402,7 +10405,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="22" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>150</v>
       </c>
@@ -10419,7 +10422,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="23" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>151</v>
       </c>
@@ -10436,7 +10439,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="24" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>152</v>
       </c>
@@ -10453,7 +10456,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="25" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>153</v>
       </c>
@@ -10470,7 +10473,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="26" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>118</v>
       </c>
@@ -10487,7 +10490,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="27" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>154</v>
       </c>
@@ -10504,7 +10507,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="28" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
         <v>117</v>
       </c>
@@ -10521,7 +10524,7 @@
         <v>216</v>
       </c>
     </row>
-    <row r="29" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
         <v>155</v>
       </c>
@@ -10538,7 +10541,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="30" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
         <v>156</v>
       </c>
@@ -10555,7 +10558,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="31" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
         <v>157</v>
       </c>
@@ -10572,7 +10575,7 @@
         <v>87.5</v>
       </c>
     </row>
-    <row r="32" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
         <v>158</v>
       </c>
@@ -10589,7 +10592,7 @@
         <v>94.6</v>
       </c>
     </row>
-    <row r="33" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
         <v>159</v>
       </c>
@@ -10606,7 +10609,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="34" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
         <v>160</v>
       </c>
@@ -10623,7 +10626,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="35" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
         <v>161</v>
       </c>
@@ -10640,7 +10643,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="36" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
         <v>162</v>
       </c>
@@ -10657,7 +10660,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="37" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
         <v>163</v>
       </c>
@@ -10674,7 +10677,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="38" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
         <v>164</v>
       </c>
@@ -10691,7 +10694,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="39" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
         <v>165</v>
       </c>
@@ -10708,7 +10711,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="40" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
         <v>114</v>
       </c>
@@ -10725,7 +10728,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="41" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
         <v>166</v>
       </c>
@@ -10742,7 +10745,7 @@
         <v>19.8</v>
       </c>
     </row>
-    <row r="42" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
         <v>167</v>
       </c>
@@ -10759,7 +10762,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="43" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
         <v>124</v>
       </c>
@@ -10776,7 +10779,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="44" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
         <v>168</v>
       </c>
@@ -10793,7 +10796,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="45" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
         <v>169</v>
       </c>
@@ -10810,7 +10813,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="46" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
         <v>170</v>
       </c>
@@ -10838,13 +10841,13 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <dimension ref="A1:E192"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="60.875" customWidth="1"/>
     <col min="2" max="5" width="20.875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>11</v>
       </c>
@@ -10861,7 +10864,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="2" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>171</v>
       </c>
@@ -10878,7 +10881,7 @@
         <v>121.6</v>
       </c>
     </row>
-    <row r="3" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>172</v>
       </c>
@@ -10895,7 +10898,7 @@
         <v>104.8</v>
       </c>
     </row>
-    <row r="4" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>173</v>
       </c>
@@ -10912,7 +10915,7 @@
         <v>63.5</v>
       </c>
     </row>
-    <row r="5" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>174</v>
       </c>
@@ -10929,7 +10932,7 @@
         <v>69.5</v>
       </c>
     </row>
-    <row r="6" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>175</v>
       </c>
@@ -10946,7 +10949,7 @@
         <v>78.8</v>
       </c>
     </row>
-    <row r="7" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>176</v>
       </c>
@@ -10963,7 +10966,7 @@
         <v>55.6</v>
       </c>
     </row>
-    <row r="8" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>177</v>
       </c>
@@ -10980,7 +10983,7 @@
         <v>138.69999999999999</v>
       </c>
     </row>
-    <row r="9" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>178</v>
       </c>
@@ -10997,7 +11000,7 @@
         <v>111.1</v>
       </c>
     </row>
-    <row r="10" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>179</v>
       </c>
@@ -11014,7 +11017,7 @@
         <v>81.400000000000006</v>
       </c>
     </row>
-    <row r="11" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>180</v>
       </c>
@@ -11031,7 +11034,7 @@
         <v>148.6</v>
       </c>
     </row>
-    <row r="12" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>181</v>
       </c>
@@ -11048,7 +11051,7 @@
         <v>111.6</v>
       </c>
     </row>
-    <row r="13" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>182</v>
       </c>
@@ -11065,7 +11068,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="14" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>183</v>
       </c>
@@ -11082,7 +11085,7 @@
         <v>102.6</v>
       </c>
     </row>
-    <row r="15" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>184</v>
       </c>
@@ -11099,7 +11102,7 @@
         <v>107.6</v>
       </c>
     </row>
-    <row r="16" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>185</v>
       </c>
@@ -11116,7 +11119,7 @@
         <v>96.1</v>
       </c>
     </row>
-    <row r="17" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>186</v>
       </c>
@@ -11133,7 +11136,7 @@
         <v>87.5</v>
       </c>
     </row>
-    <row r="18" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>187</v>
       </c>
@@ -11150,7 +11153,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="19" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>188</v>
       </c>
@@ -11167,7 +11170,7 @@
         <v>77.400000000000006</v>
       </c>
     </row>
-    <row r="20" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>189</v>
       </c>
@@ -11184,7 +11187,7 @@
         <v>62.9</v>
       </c>
     </row>
-    <row r="21" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>190</v>
       </c>
@@ -11201,7 +11204,7 @@
         <v>64.900000000000006</v>
       </c>
     </row>
-    <row r="22" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>191</v>
       </c>
@@ -11218,7 +11221,7 @@
         <v>68.8</v>
       </c>
     </row>
-    <row r="23" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>192</v>
       </c>
@@ -11235,7 +11238,7 @@
         <v>73.8</v>
       </c>
     </row>
-    <row r="24" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>193</v>
       </c>
@@ -11252,7 +11255,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="25" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>194</v>
       </c>
@@ -11269,7 +11272,7 @@
         <v>81.599999999999994</v>
       </c>
     </row>
-    <row r="26" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>195</v>
       </c>
@@ -11286,7 +11289,7 @@
         <v>60.2</v>
       </c>
     </row>
-    <row r="27" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>196</v>
       </c>
@@ -11303,7 +11306,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="28" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
         <v>197</v>
       </c>
@@ -11320,7 +11323,7 @@
         <v>60.6</v>
       </c>
     </row>
-    <row r="29" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
         <v>198</v>
       </c>
@@ -11337,7 +11340,7 @@
         <v>85.5</v>
       </c>
     </row>
-    <row r="30" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
         <v>199</v>
       </c>
@@ -11354,7 +11357,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="31" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
         <v>200</v>
       </c>
@@ -11371,7 +11374,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="32" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
         <v>201</v>
       </c>
@@ -11388,7 +11391,7 @@
         <v>40.700000000000003</v>
       </c>
     </row>
-    <row r="33" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
         <v>202</v>
       </c>
@@ -11405,7 +11408,7 @@
         <v>88.8</v>
       </c>
     </row>
-    <row r="34" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
         <v>203</v>
       </c>
@@ -11422,7 +11425,7 @@
         <v>51.8</v>
       </c>
     </row>
-    <row r="35" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
         <v>204</v>
       </c>
@@ -11439,7 +11442,7 @@
         <v>48.8</v>
       </c>
     </row>
-    <row r="36" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
         <v>205</v>
       </c>
@@ -11456,7 +11459,7 @@
         <v>37.5</v>
       </c>
     </row>
-    <row r="37" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
         <v>206</v>
       </c>
@@ -11473,7 +11476,7 @@
         <v>45.9</v>
       </c>
     </row>
-    <row r="38" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
         <v>207</v>
       </c>
@@ -11490,7 +11493,7 @@
         <v>54.3</v>
       </c>
     </row>
-    <row r="39" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
         <v>208</v>
       </c>
@@ -11507,7 +11510,7 @@
         <v>43.7</v>
       </c>
     </row>
-    <row r="40" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
         <v>209</v>
       </c>
@@ -11524,7 +11527,7 @@
         <v>48.1</v>
       </c>
     </row>
-    <row r="41" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
         <v>210</v>
       </c>
@@ -11541,7 +11544,7 @@
         <v>52.2</v>
       </c>
     </row>
-    <row r="42" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
         <v>211</v>
       </c>
@@ -11558,7 +11561,7 @@
         <v>57.3</v>
       </c>
     </row>
-    <row r="43" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
         <v>212</v>
       </c>
@@ -11575,7 +11578,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="44" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
         <v>213</v>
       </c>
@@ -11592,7 +11595,7 @@
         <v>84.6</v>
       </c>
     </row>
-    <row r="45" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
         <v>214</v>
       </c>
@@ -11609,7 +11612,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="46" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
         <v>215</v>
       </c>
@@ -11626,7 +11629,7 @@
         <v>29.6</v>
       </c>
     </row>
-    <row r="47" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
         <v>216</v>
       </c>
@@ -11643,7 +11646,7 @@
         <v>27.5</v>
       </c>
     </row>
-    <row r="48" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
         <v>217</v>
       </c>
@@ -11660,7 +11663,7 @@
         <v>20.100000000000001</v>
       </c>
     </row>
-    <row r="49" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
         <v>218</v>
       </c>
@@ -11677,7 +11680,7 @@
         <v>21.8</v>
       </c>
     </row>
-    <row r="50" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
         <v>219</v>
       </c>
@@ -11694,7 +11697,7 @@
         <v>30.5</v>
       </c>
     </row>
-    <row r="51" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
         <v>220</v>
       </c>
@@ -11711,7 +11714,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="52" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
         <v>221</v>
       </c>
@@ -11728,7 +11731,7 @@
         <v>60.1</v>
       </c>
     </row>
-    <row r="53" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
         <v>222</v>
       </c>
@@ -11745,7 +11748,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="54" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
         <v>223</v>
       </c>
@@ -11762,7 +11765,7 @@
         <v>80.7</v>
       </c>
     </row>
-    <row r="55" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
         <v>224</v>
       </c>
@@ -11779,7 +11782,7 @@
         <v>79.099999999999994</v>
       </c>
     </row>
-    <row r="56" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
         <v>225</v>
       </c>
@@ -11796,7 +11799,7 @@
         <v>80.8</v>
       </c>
     </row>
-    <row r="57" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
         <v>226</v>
       </c>
@@ -11813,7 +11816,7 @@
         <v>62.3</v>
       </c>
     </row>
-    <row r="58" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
         <v>227</v>
       </c>
@@ -11830,7 +11833,7 @@
         <v>44.5</v>
       </c>
     </row>
-    <row r="59" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
         <v>228</v>
       </c>
@@ -11847,7 +11850,7 @@
         <v>41.2</v>
       </c>
     </row>
-    <row r="60" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
         <v>229</v>
       </c>
@@ -11864,7 +11867,7 @@
         <v>43.4</v>
       </c>
     </row>
-    <row r="61" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
         <v>230</v>
       </c>
@@ -11881,7 +11884,7 @@
         <v>41.1</v>
       </c>
     </row>
-    <row r="62" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
         <v>231</v>
       </c>
@@ -11898,7 +11901,7 @@
         <v>41.7</v>
       </c>
     </row>
-    <row r="63" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
         <v>232</v>
       </c>
@@ -11915,7 +11918,7 @@
         <v>32.299999999999997</v>
       </c>
     </row>
-    <row r="64" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
         <v>233</v>
       </c>
@@ -11932,7 +11935,7 @@
         <v>42.4</v>
       </c>
     </row>
-    <row r="65" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
         <v>234</v>
       </c>
@@ -11949,7 +11952,7 @@
         <v>34.700000000000003</v>
       </c>
     </row>
-    <row r="66" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
         <v>235</v>
       </c>
@@ -11966,7 +11969,7 @@
         <v>26.6</v>
       </c>
     </row>
-    <row r="67" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
         <v>236</v>
       </c>
@@ -11983,7 +11986,7 @@
         <v>26.8</v>
       </c>
     </row>
-    <row r="68" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
         <v>237</v>
       </c>
@@ -12000,7 +12003,7 @@
         <v>66.5</v>
       </c>
     </row>
-    <row r="69" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
         <v>238</v>
       </c>
@@ -12017,7 +12020,7 @@
         <v>49.3</v>
       </c>
     </row>
-    <row r="70" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
         <v>239</v>
       </c>
@@ -12034,7 +12037,7 @@
         <v>41.3</v>
       </c>
     </row>
-    <row r="71" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
         <v>240</v>
       </c>
@@ -12051,7 +12054,7 @@
         <v>37.200000000000003</v>
       </c>
     </row>
-    <row r="72" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
         <v>241</v>
       </c>
@@ -12068,7 +12071,7 @@
         <v>46.2</v>
       </c>
     </row>
-    <row r="73" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
         <v>242</v>
       </c>
@@ -12085,7 +12088,7 @@
         <v>38.6</v>
       </c>
     </row>
-    <row r="74" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
         <v>243</v>
       </c>
@@ -12102,7 +12105,7 @@
         <v>10.9</v>
       </c>
     </row>
-    <row r="75" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
         <v>244</v>
       </c>
@@ -12119,7 +12122,7 @@
         <v>9.5</v>
       </c>
     </row>
-    <row r="76" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
         <v>245</v>
       </c>
@@ -12136,7 +12139,7 @@
         <v>8.1</v>
       </c>
     </row>
-    <row r="77" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
         <v>246</v>
       </c>
@@ -12153,7 +12156,7 @@
         <v>70.400000000000006</v>
       </c>
     </row>
-    <row r="78" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
         <v>247</v>
       </c>
@@ -12170,7 +12173,7 @@
         <v>61.9</v>
       </c>
     </row>
-    <row r="79" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
         <v>248</v>
       </c>
@@ -12187,7 +12190,7 @@
         <v>55.1</v>
       </c>
     </row>
-    <row r="80" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
         <v>249</v>
       </c>
@@ -12204,7 +12207,7 @@
         <v>53.2</v>
       </c>
     </row>
-    <row r="81" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
         <v>250</v>
       </c>
@@ -12221,7 +12224,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="82" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
         <v>251</v>
       </c>
@@ -12238,7 +12241,7 @@
         <v>46.7</v>
       </c>
     </row>
-    <row r="83" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
         <v>252</v>
       </c>
@@ -12255,7 +12258,7 @@
         <v>41.8</v>
       </c>
     </row>
-    <row r="84" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A84" t="s">
         <v>253</v>
       </c>
@@ -12272,7 +12275,7 @@
         <v>35.1</v>
       </c>
     </row>
-    <row r="85" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
         <v>254</v>
       </c>
@@ -12289,7 +12292,7 @@
         <v>20.399999999999999</v>
       </c>
     </row>
-    <row r="86" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A86" t="s">
         <v>255</v>
       </c>
@@ -12306,7 +12309,7 @@
         <v>22.3</v>
       </c>
     </row>
-    <row r="87" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A87" t="s">
         <v>256</v>
       </c>
@@ -12323,7 +12326,7 @@
         <v>21.6</v>
       </c>
     </row>
-    <row r="88" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A88" t="s">
         <v>257</v>
       </c>
@@ -12340,7 +12343,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="89" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A89" t="s">
         <v>258</v>
       </c>
@@ -12357,7 +12360,7 @@
         <v>20.100000000000001</v>
       </c>
     </row>
-    <row r="90" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A90" t="s">
         <v>259</v>
       </c>
@@ -12374,7 +12377,7 @@
         <v>25.8</v>
       </c>
     </row>
-    <row r="91" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A91" t="s">
         <v>260</v>
       </c>
@@ -12391,7 +12394,7 @@
         <v>18.600000000000001</v>
       </c>
     </row>
-    <row r="92" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A92" t="s">
         <v>261</v>
       </c>
@@ -12408,7 +12411,7 @@
         <v>22.2</v>
       </c>
     </row>
-    <row r="93" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A93" t="s">
         <v>262</v>
       </c>
@@ -12425,7 +12428,7 @@
         <v>23.1</v>
       </c>
     </row>
-    <row r="94" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A94" t="s">
         <v>263</v>
       </c>
@@ -12442,7 +12445,7 @@
         <v>21.4</v>
       </c>
     </row>
-    <row r="95" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A95" t="s">
         <v>264</v>
       </c>
@@ -12459,7 +12462,7 @@
         <v>22.8</v>
       </c>
     </row>
-    <row r="96" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A96" t="s">
         <v>265</v>
       </c>
@@ -12476,7 +12479,7 @@
         <v>23.7</v>
       </c>
     </row>
-    <row r="97" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A97" t="s">
         <v>266</v>
       </c>
@@ -12493,7 +12496,7 @@
         <v>30.6</v>
       </c>
     </row>
-    <row r="98" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A98" t="s">
         <v>267</v>
       </c>
@@ -12510,7 +12513,7 @@
         <v>21.2</v>
       </c>
     </row>
-    <row r="99" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A99" t="s">
         <v>268</v>
       </c>
@@ -12527,7 +12530,7 @@
         <v>23.5</v>
       </c>
     </row>
-    <row r="100" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A100" t="s">
         <v>268</v>
       </c>
@@ -12544,7 +12547,7 @@
         <v>27.7</v>
       </c>
     </row>
-    <row r="101" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A101" t="s">
         <v>269</v>
       </c>
@@ -12561,7 +12564,7 @@
         <v>160.30000000000001</v>
       </c>
     </row>
-    <row r="102" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A102" t="s">
         <v>270</v>
       </c>
@@ -12578,7 +12581,7 @@
         <v>106.2</v>
       </c>
     </row>
-    <row r="103" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A103" t="s">
         <v>271</v>
       </c>
@@ -12595,7 +12598,7 @@
         <v>79.900000000000006</v>
       </c>
     </row>
-    <row r="104" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A104" t="s">
         <v>272</v>
       </c>
@@ -12612,7 +12615,7 @@
         <v>79.2</v>
       </c>
     </row>
-    <row r="105" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A105" t="s">
         <v>273</v>
       </c>
@@ -12629,7 +12632,7 @@
         <v>72.900000000000006</v>
       </c>
     </row>
-    <row r="106" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A106" t="s">
         <v>274</v>
       </c>
@@ -12646,7 +12649,7 @@
         <v>91.8</v>
       </c>
     </row>
-    <row r="107" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A107" t="s">
         <v>275</v>
       </c>
@@ -12663,7 +12666,7 @@
         <v>71.900000000000006</v>
       </c>
     </row>
-    <row r="108" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A108" t="s">
         <v>276</v>
       </c>
@@ -12680,7 +12683,7 @@
         <v>71.900000000000006</v>
       </c>
     </row>
-    <row r="109" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A109" t="s">
         <v>277</v>
       </c>
@@ -12697,7 +12700,7 @@
         <v>66.7</v>
       </c>
     </row>
-    <row r="110" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A110" t="s">
         <v>278</v>
       </c>
@@ -12714,7 +12717,7 @@
         <v>62.4</v>
       </c>
     </row>
-    <row r="111" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A111" t="s">
         <v>279</v>
       </c>
@@ -12731,7 +12734,7 @@
         <v>62.8</v>
       </c>
     </row>
-    <row r="112" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A112" t="s">
         <v>280</v>
       </c>
@@ -12748,7 +12751,7 @@
         <v>60.9</v>
       </c>
     </row>
-    <row r="113" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A113" t="s">
         <v>281</v>
       </c>
@@ -12765,7 +12768,7 @@
         <v>41.6</v>
       </c>
     </row>
-    <row r="114" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A114" t="s">
         <v>282</v>
       </c>
@@ -12782,7 +12785,7 @@
         <v>122.2</v>
       </c>
     </row>
-    <row r="115" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A115" t="s">
         <v>283</v>
       </c>
@@ -12799,7 +12802,7 @@
         <v>106.2</v>
       </c>
     </row>
-    <row r="116" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A116" t="s">
         <v>284</v>
       </c>
@@ -12816,7 +12819,7 @@
         <v>64.099999999999994</v>
       </c>
     </row>
-    <row r="117" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A117" t="s">
         <v>285</v>
       </c>
@@ -12833,7 +12836,7 @@
         <v>70.599999999999994</v>
       </c>
     </row>
-    <row r="118" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A118" t="s">
         <v>286</v>
       </c>
@@ -12850,7 +12853,7 @@
         <v>80.400000000000006</v>
       </c>
     </row>
-    <row r="119" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A119" t="s">
         <v>287</v>
       </c>
@@ -12867,7 +12870,7 @@
         <v>55.9</v>
       </c>
     </row>
-    <row r="120" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A120" t="s">
         <v>288</v>
       </c>
@@ -12884,7 +12887,7 @@
         <v>138.69999999999999</v>
       </c>
     </row>
-    <row r="121" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A121" t="s">
         <v>289</v>
       </c>
@@ -12901,7 +12904,7 @@
         <v>111.1</v>
       </c>
     </row>
-    <row r="122" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A122" t="s">
         <v>290</v>
       </c>
@@ -12918,7 +12921,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="123" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A123" t="s">
         <v>291</v>
       </c>
@@ -12935,7 +12938,7 @@
         <v>149.9</v>
       </c>
     </row>
-    <row r="124" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A124" t="s">
         <v>292</v>
       </c>
@@ -12952,7 +12955,7 @@
         <v>113.8</v>
       </c>
     </row>
-    <row r="125" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A125" t="s">
         <v>293</v>
       </c>
@@ -12969,7 +12972,7 @@
         <v>124.5</v>
       </c>
     </row>
-    <row r="126" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A126" t="s">
         <v>294</v>
       </c>
@@ -12986,7 +12989,7 @@
         <v>103.3</v>
       </c>
     </row>
-    <row r="127" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A127" t="s">
         <v>295</v>
       </c>
@@ -13003,7 +13006,7 @@
         <v>107.3</v>
       </c>
     </row>
-    <row r="128" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="128" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A128" t="s">
         <v>296</v>
       </c>
@@ -13020,7 +13023,7 @@
         <v>96.1</v>
       </c>
     </row>
-    <row r="129" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="129" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A129" t="s">
         <v>297</v>
       </c>
@@ -13037,7 +13040,7 @@
         <v>88.6</v>
       </c>
     </row>
-    <row r="130" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="130" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A130" t="s">
         <v>298</v>
       </c>
@@ -13054,7 +13057,7 @@
         <v>90.5</v>
       </c>
     </row>
-    <row r="131" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="131" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A131" t="s">
         <v>299</v>
       </c>
@@ -13071,7 +13074,7 @@
         <v>77.900000000000006</v>
       </c>
     </row>
-    <row r="132" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="132" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A132" t="s">
         <v>300</v>
       </c>
@@ -13088,7 +13091,7 @@
         <v>63.1</v>
       </c>
     </row>
-    <row r="133" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="133" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A133" t="s">
         <v>301</v>
       </c>
@@ -13105,7 +13108,7 @@
         <v>65.2</v>
       </c>
     </row>
-    <row r="134" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="134" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A134" t="s">
         <v>302</v>
       </c>
@@ -13122,7 +13125,7 @@
         <v>69.2</v>
       </c>
     </row>
-    <row r="135" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="135" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A135" t="s">
         <v>303</v>
       </c>
@@ -13139,7 +13142,7 @@
         <v>74.2</v>
       </c>
     </row>
-    <row r="136" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="136" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A136" t="s">
         <v>304</v>
       </c>
@@ -13156,7 +13159,7 @@
         <v>71.3</v>
       </c>
     </row>
-    <row r="137" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="137" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A137" t="s">
         <v>305</v>
       </c>
@@ -13173,7 +13176,7 @@
         <v>82.1</v>
       </c>
     </row>
-    <row r="138" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="138" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A138" t="s">
         <v>306</v>
       </c>
@@ -13190,7 +13193,7 @@
         <v>60.3</v>
       </c>
     </row>
-    <row r="139" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="139" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A139" t="s">
         <v>307</v>
       </c>
@@ -13207,7 +13210,7 @@
         <v>69.2</v>
       </c>
     </row>
-    <row r="140" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="140" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A140" t="s">
         <v>308</v>
       </c>
@@ -13224,7 +13227,7 @@
         <v>60.7</v>
       </c>
     </row>
-    <row r="141" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="141" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A141" t="s">
         <v>309</v>
       </c>
@@ -13241,7 +13244,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="142" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="142" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A142" t="s">
         <v>310</v>
       </c>
@@ -13258,7 +13261,7 @@
         <v>52.1</v>
       </c>
     </row>
-    <row r="143" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="143" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A143" t="s">
         <v>311</v>
       </c>
@@ -13275,7 +13278,7 @@
         <v>49.1</v>
       </c>
     </row>
-    <row r="144" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="144" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A144" t="s">
         <v>312</v>
       </c>
@@ -13292,7 +13295,7 @@
         <v>38.299999999999997</v>
       </c>
     </row>
-    <row r="145" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="145" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A145" t="s">
         <v>313</v>
       </c>
@@ -13309,7 +13312,7 @@
         <v>44.8</v>
       </c>
     </row>
-    <row r="146" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="146" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A146" t="s">
         <v>314</v>
       </c>
@@ -13326,7 +13329,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="147" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="147" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A147" t="s">
         <v>315</v>
       </c>
@@ -13343,7 +13346,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="148" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="148" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A148" t="s">
         <v>316</v>
       </c>
@@ -13360,7 +13363,7 @@
         <v>41.6</v>
       </c>
     </row>
-    <row r="149" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="149" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A149" t="s">
         <v>317</v>
       </c>
@@ -13377,7 +13380,7 @@
         <v>43.4</v>
       </c>
     </row>
-    <row r="150" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="150" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A150" t="s">
         <v>318</v>
       </c>
@@ -13394,7 +13397,7 @@
         <v>32.700000000000003</v>
       </c>
     </row>
-    <row r="151" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="151" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A151" t="s">
         <v>319</v>
       </c>
@@ -13411,7 +13414,7 @@
         <v>43.7</v>
       </c>
     </row>
-    <row r="152" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="152" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A152" t="s">
         <v>320</v>
       </c>
@@ -13428,7 +13431,7 @@
         <v>35.700000000000003</v>
       </c>
     </row>
-    <row r="153" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="153" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A153" t="s">
         <v>321</v>
       </c>
@@ -13445,7 +13448,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="154" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="154" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A154" t="s">
         <v>322</v>
       </c>
@@ -13462,7 +13465,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="155" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="155" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A155" t="s">
         <v>323</v>
       </c>
@@ -13479,7 +13482,7 @@
         <v>72.900000000000006</v>
       </c>
     </row>
-    <row r="156" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="156" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A156" t="s">
         <v>324</v>
       </c>
@@ -13496,7 +13499,7 @@
         <v>54.9</v>
       </c>
     </row>
-    <row r="157" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="157" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A157" t="s">
         <v>325</v>
       </c>
@@ -13513,7 +13516,7 @@
         <v>41.3</v>
       </c>
     </row>
-    <row r="158" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="158" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A158" t="s">
         <v>326</v>
       </c>
@@ -13530,7 +13533,7 @@
         <v>36.9</v>
       </c>
     </row>
-    <row r="159" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="159" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A159" t="s">
         <v>327</v>
       </c>
@@ -13547,7 +13550,7 @@
         <v>48.5</v>
       </c>
     </row>
-    <row r="160" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="160" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A160" t="s">
         <v>328</v>
       </c>
@@ -13564,7 +13567,7 @@
         <v>39.200000000000003</v>
       </c>
     </row>
-    <row r="161" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="161" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A161" t="s">
         <v>329</v>
       </c>
@@ -13581,7 +13584,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="162" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="162" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A162" t="s">
         <v>330</v>
       </c>
@@ -13598,7 +13601,7 @@
         <v>9.6</v>
       </c>
     </row>
-    <row r="163" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="163" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A163" t="s">
         <v>331</v>
       </c>
@@ -13615,7 +13618,7 @@
         <v>8.1</v>
       </c>
     </row>
-    <row r="164" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="164" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A164" t="s">
         <v>332</v>
       </c>
@@ -13632,7 +13635,7 @@
         <v>20.6</v>
       </c>
     </row>
-    <row r="165" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="165" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A165" t="s">
         <v>333</v>
       </c>
@@ -13649,7 +13652,7 @@
         <v>22.6</v>
       </c>
     </row>
-    <row r="166" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="166" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A166" t="s">
         <v>334</v>
       </c>
@@ -13666,7 +13669,7 @@
         <v>21.9</v>
       </c>
     </row>
-    <row r="167" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="167" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A167" t="s">
         <v>335</v>
       </c>
@@ -13683,7 +13686,7 @@
         <v>22.8</v>
       </c>
     </row>
-    <row r="168" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="168" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A168" t="s">
         <v>336</v>
       </c>
@@ -13700,7 +13703,7 @@
         <v>20.7</v>
       </c>
     </row>
-    <row r="169" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="169" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A169" t="s">
         <v>337</v>
       </c>
@@ -13717,7 +13720,7 @@
         <v>26.6</v>
       </c>
     </row>
-    <row r="170" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="170" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A170" t="s">
         <v>338</v>
       </c>
@@ -13734,7 +13737,7 @@
         <v>18.899999999999999</v>
       </c>
     </row>
-    <row r="171" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="171" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A171" t="s">
         <v>339</v>
       </c>
@@ -13751,7 +13754,7 @@
         <v>22.7</v>
       </c>
     </row>
-    <row r="172" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="172" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A172" t="s">
         <v>340</v>
       </c>
@@ -13768,7 +13771,7 @@
         <v>23.2</v>
       </c>
     </row>
-    <row r="173" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="173" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A173" t="s">
         <v>341</v>
       </c>
@@ -13785,7 +13788,7 @@
         <v>21.3</v>
       </c>
     </row>
-    <row r="174" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="174" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A174" t="s">
         <v>342</v>
       </c>
@@ -13802,7 +13805,7 @@
         <v>24.1</v>
       </c>
     </row>
-    <row r="175" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="175" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A175" t="s">
         <v>343</v>
       </c>
@@ -13819,7 +13822,7 @@
         <v>31.1</v>
       </c>
     </row>
-    <row r="176" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="176" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A176" t="s">
         <v>344</v>
       </c>
@@ -13836,7 +13839,7 @@
         <v>22.4</v>
       </c>
     </row>
-    <row r="177" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="177" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A177" t="s">
         <v>345</v>
       </c>
@@ -13853,7 +13856,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="178" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="178" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A178" t="s">
         <v>346</v>
       </c>
@@ -13870,7 +13873,7 @@
         <v>161</v>
       </c>
     </row>
-    <row r="179" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="179" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A179" t="s">
         <v>347</v>
       </c>
@@ -13887,7 +13890,7 @@
         <v>107.3</v>
       </c>
     </row>
-    <row r="180" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="180" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A180" t="s">
         <v>348</v>
       </c>
@@ -13904,7 +13907,7 @@
         <v>80.599999999999994</v>
       </c>
     </row>
-    <row r="181" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="181" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A181" t="s">
         <v>349</v>
       </c>
@@ -13921,7 +13924,7 @@
         <v>74.900000000000006</v>
       </c>
     </row>
-    <row r="182" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="182" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A182" t="s">
         <v>350</v>
       </c>
@@ -13938,7 +13941,7 @@
         <v>94.5</v>
       </c>
     </row>
-    <row r="183" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="183" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A183" t="s">
         <v>351</v>
       </c>
@@ -13955,7 +13958,7 @@
         <v>72.599999999999994</v>
       </c>
     </row>
-    <row r="184" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="184" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A184" t="s">
         <v>352</v>
       </c>
@@ -13972,7 +13975,7 @@
         <v>72.599999999999994</v>
       </c>
     </row>
-    <row r="185" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="185" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A185" t="s">
         <v>353</v>
       </c>
@@ -13989,7 +13992,7 @@
         <v>67.400000000000006</v>
       </c>
     </row>
-    <row r="186" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="186" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A186" t="s">
         <v>354</v>
       </c>
@@ -14006,7 +14009,7 @@
         <v>64.3</v>
       </c>
     </row>
-    <row r="187" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="187" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A187" t="s">
         <v>355</v>
       </c>
@@ -14023,7 +14026,7 @@
         <v>64.900000000000006</v>
       </c>
     </row>
-    <row r="188" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="188" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A188" t="s">
         <v>356</v>
       </c>
@@ -14040,7 +14043,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="189" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="189" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A189" t="s">
         <v>357</v>
       </c>
@@ -14057,7 +14060,7 @@
         <v>42.2</v>
       </c>
     </row>
-    <row r="190" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="190" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A190" t="s">
         <v>358</v>
       </c>
@@ -14074,7 +14077,7 @@
         <v>140.1</v>
       </c>
     </row>
-    <row r="191" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="191" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A191" t="s">
         <v>359</v>
       </c>
@@ -14091,7 +14094,7 @@
         <v>38.5</v>
       </c>
     </row>
-    <row r="192" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="192" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A192" t="s">
         <v>360</v>
       </c>
@@ -14119,13 +14122,13 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
   <dimension ref="A1:E34"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="60.875" customWidth="1"/>
     <col min="2" max="5" width="20.875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>11</v>
       </c>
@@ -14142,7 +14145,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="2" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>361</v>
       </c>
@@ -14159,7 +14162,7 @@
         <v>17.8</v>
       </c>
     </row>
-    <row r="3" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>362</v>
       </c>
@@ -14176,7 +14179,7 @@
         <v>12.9</v>
       </c>
     </row>
-    <row r="4" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>363</v>
       </c>
@@ -14193,7 +14196,7 @@
         <v>15.7</v>
       </c>
     </row>
-    <row r="5" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>364</v>
       </c>
@@ -14210,7 +14213,7 @@
         <v>9.6</v>
       </c>
     </row>
-    <row r="6" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>365</v>
       </c>
@@ -14227,7 +14230,7 @@
         <v>6.1</v>
       </c>
     </row>
-    <row r="7" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>366</v>
       </c>
@@ -14244,7 +14247,7 @@
         <v>6.9</v>
       </c>
     </row>
-    <row r="8" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>367</v>
       </c>
@@ -14261,7 +14264,7 @@
         <v>7.7</v>
       </c>
     </row>
-    <row r="9" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>368</v>
       </c>
@@ -14278,7 +14281,7 @@
         <v>6.7</v>
       </c>
     </row>
-    <row r="10" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>369</v>
       </c>
@@ -14295,7 +14298,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="11" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>370</v>
       </c>
@@ -14312,7 +14315,7 @@
         <v>7.9</v>
       </c>
     </row>
-    <row r="12" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>371</v>
       </c>
@@ -14329,7 +14332,7 @@
         <v>6.9</v>
       </c>
     </row>
-    <row r="13" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>372</v>
       </c>
@@ -14346,7 +14349,7 @@
         <v>7.1</v>
       </c>
     </row>
-    <row r="14" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>373</v>
       </c>
@@ -14363,7 +14366,7 @@
         <v>10.3</v>
       </c>
     </row>
-    <row r="15" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>374</v>
       </c>
@@ -14380,7 +14383,7 @@
         <v>15.5</v>
       </c>
     </row>
-    <row r="16" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>375</v>
       </c>
@@ -14397,7 +14400,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="17" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>376</v>
       </c>
@@ -14414,7 +14417,7 @@
         <v>12.4</v>
       </c>
     </row>
-    <row r="18" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>377</v>
       </c>
@@ -14431,7 +14434,7 @@
         <v>12.4</v>
       </c>
     </row>
-    <row r="19" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>378</v>
       </c>
@@ -14448,7 +14451,7 @@
         <v>12.6</v>
       </c>
     </row>
-    <row r="20" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>379</v>
       </c>
@@ -14465,7 +14468,7 @@
         <v>12.3</v>
       </c>
     </row>
-    <row r="21" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>380</v>
       </c>
@@ -14482,7 +14485,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="22" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>381</v>
       </c>
@@ -14499,7 +14502,7 @@
         <v>12.1</v>
       </c>
     </row>
-    <row r="23" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>382</v>
       </c>
@@ -14516,7 +14519,7 @@
         <v>13.6</v>
       </c>
     </row>
-    <row r="24" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>383</v>
       </c>
@@ -14533,7 +14536,7 @@
         <v>10.3</v>
       </c>
     </row>
-    <row r="25" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>384</v>
       </c>
@@ -14550,7 +14553,7 @@
         <v>12.4</v>
       </c>
     </row>
-    <row r="26" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>385</v>
       </c>
@@ -14567,7 +14570,7 @@
         <v>8.5</v>
       </c>
     </row>
-    <row r="27" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>386</v>
       </c>
@@ -14584,7 +14587,7 @@
         <v>11.7</v>
       </c>
     </row>
-    <row r="28" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
         <v>387</v>
       </c>
@@ -14601,7 +14604,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="29" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
         <v>388</v>
       </c>
@@ -14618,7 +14621,7 @@
         <v>12.4</v>
       </c>
     </row>
-    <row r="30" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
         <v>389</v>
       </c>
@@ -14635,7 +14638,7 @@
         <v>16.3</v>
       </c>
     </row>
-    <row r="31" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
         <v>390</v>
       </c>
@@ -14652,7 +14655,7 @@
         <v>4.0999999999999996</v>
       </c>
     </row>
-    <row r="32" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
         <v>391</v>
       </c>
@@ -14669,7 +14672,7 @@
         <v>9.3000000000000007</v>
       </c>
     </row>
-    <row r="33" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
         <v>392</v>
       </c>
@@ -14686,7 +14689,7 @@
         <v>15.7</v>
       </c>
     </row>
-    <row r="34" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
         <v>393</v>
       </c>
@@ -14714,13 +14717,13 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
   <dimension ref="A1:G8"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="60.875" customWidth="1"/>
     <col min="2" max="7" width="20.875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>394</v>
       </c>
@@ -14743,7 +14746,7 @@
         <v>398</v>
       </c>
     </row>
-    <row r="2" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>399</v>
       </c>
@@ -14763,7 +14766,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>400</v>
       </c>
@@ -14783,7 +14786,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>401</v>
       </c>
@@ -14803,7 +14806,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>402</v>
       </c>
@@ -14823,7 +14826,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>403</v>
       </c>
@@ -14843,7 +14846,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>404</v>
       </c>
@@ -14863,7 +14866,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>405</v>
       </c>
@@ -14894,13 +14897,13 @@
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0700-000000000000}">
   <dimension ref="A1:E45"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="60.875" customWidth="1"/>
     <col min="2" max="5" width="20.875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>11</v>
       </c>
@@ -14917,7 +14920,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="2" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>406</v>
       </c>
@@ -14934,7 +14937,7 @@
         <v>212</v>
       </c>
     </row>
-    <row r="3" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>407</v>
       </c>
@@ -14951,7 +14954,7 @@
         <v>152.30000000000001</v>
       </c>
     </row>
-    <row r="4" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>408</v>
       </c>
@@ -14968,7 +14971,7 @@
         <v>101.2</v>
       </c>
     </row>
-    <row r="5" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>409</v>
       </c>
@@ -14985,7 +14988,7 @@
         <v>90.5</v>
       </c>
     </row>
-    <row r="6" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>410</v>
       </c>
@@ -15002,7 +15005,7 @@
         <v>127.4</v>
       </c>
     </row>
-    <row r="7" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>411</v>
       </c>
@@ -15019,7 +15022,7 @@
         <v>91.5</v>
       </c>
     </row>
-    <row r="8" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>412</v>
       </c>
@@ -15036,7 +15039,7 @@
         <v>122.7</v>
       </c>
     </row>
-    <row r="9" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>413</v>
       </c>
@@ -15053,7 +15056,7 @@
         <v>115.2</v>
       </c>
     </row>
-    <row r="10" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>414</v>
       </c>
@@ -15070,7 +15073,7 @@
         <v>101.1</v>
       </c>
     </row>
-    <row r="11" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>415</v>
       </c>
@@ -15087,7 +15090,7 @@
         <v>122.4</v>
       </c>
     </row>
-    <row r="12" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>416</v>
       </c>
@@ -15104,7 +15107,7 @@
         <v>100.8</v>
       </c>
     </row>
-    <row r="13" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>417</v>
       </c>
@@ -15121,7 +15124,7 @@
         <v>103.6</v>
       </c>
     </row>
-    <row r="14" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>418</v>
       </c>
@@ -15138,7 +15141,7 @@
         <v>109.4</v>
       </c>
     </row>
-    <row r="15" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>419</v>
       </c>
@@ -15155,7 +15158,7 @@
         <v>115.7</v>
       </c>
     </row>
-    <row r="16" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>420</v>
       </c>
@@ -15172,7 +15175,7 @@
         <v>94.4</v>
       </c>
     </row>
-    <row r="17" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>421</v>
       </c>
@@ -15189,7 +15192,7 @@
         <v>111.4</v>
       </c>
     </row>
-    <row r="18" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>422</v>
       </c>
@@ -15206,7 +15209,7 @@
         <v>91.2</v>
       </c>
     </row>
-    <row r="19" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>423</v>
       </c>
@@ -15223,7 +15226,7 @@
         <v>95.2</v>
       </c>
     </row>
-    <row r="20" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>424</v>
       </c>
@@ -15240,7 +15243,7 @@
         <v>99.7</v>
       </c>
     </row>
-    <row r="21" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>425</v>
       </c>
@@ -15257,7 +15260,7 @@
         <v>98.7</v>
       </c>
     </row>
-    <row r="22" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>426</v>
       </c>
@@ -15274,7 +15277,7 @@
         <v>103.7</v>
       </c>
     </row>
-    <row r="23" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>427</v>
       </c>
@@ -15291,7 +15294,7 @@
         <v>87.6</v>
       </c>
     </row>
-    <row r="24" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>428</v>
       </c>
@@ -15308,7 +15311,7 @@
         <v>90.7</v>
       </c>
     </row>
-    <row r="25" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>429</v>
       </c>
@@ -15325,7 +15328,7 @@
         <v>92.9</v>
       </c>
     </row>
-    <row r="26" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>430</v>
       </c>
@@ -15342,7 +15345,7 @@
         <v>93.4</v>
       </c>
     </row>
-    <row r="27" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>431</v>
       </c>
@@ -15359,7 +15362,7 @@
         <v>95.7</v>
       </c>
     </row>
-    <row r="28" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
         <v>432</v>
       </c>
@@ -15376,7 +15379,7 @@
         <v>97.8</v>
       </c>
     </row>
-    <row r="29" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
         <v>433</v>
       </c>
@@ -15393,7 +15396,7 @@
         <v>100.1</v>
       </c>
     </row>
-    <row r="30" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
         <v>434</v>
       </c>
@@ -15410,7 +15413,7 @@
         <v>100.9</v>
       </c>
     </row>
-    <row r="31" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
         <v>435</v>
       </c>
@@ -15427,7 +15430,7 @@
         <v>86.5</v>
       </c>
     </row>
-    <row r="32" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
         <v>436</v>
       </c>
@@ -15444,7 +15447,7 @@
         <v>73.5</v>
       </c>
     </row>
-    <row r="33" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
         <v>437</v>
       </c>
@@ -15461,7 +15464,7 @@
         <v>74.5</v>
       </c>
     </row>
-    <row r="34" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
         <v>438</v>
       </c>
@@ -15478,7 +15481,7 @@
         <v>139</v>
       </c>
     </row>
-    <row r="35" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
         <v>439</v>
       </c>
@@ -15495,7 +15498,7 @@
         <v>79.3</v>
       </c>
     </row>
-    <row r="36" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
         <v>440</v>
       </c>
@@ -15512,7 +15515,7 @@
         <v>58.8</v>
       </c>
     </row>
-    <row r="37" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
         <v>441</v>
       </c>
@@ -15529,7 +15532,7 @@
         <v>49.6</v>
       </c>
     </row>
-    <row r="38" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
         <v>442</v>
       </c>
@@ -15546,7 +15549,7 @@
         <v>59.6</v>
       </c>
     </row>
-    <row r="39" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
         <v>443</v>
       </c>
@@ -15563,7 +15566,7 @@
         <v>70.5</v>
       </c>
     </row>
-    <row r="40" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
         <v>444</v>
       </c>
@@ -15580,7 +15583,7 @@
         <v>53.6</v>
       </c>
     </row>
-    <row r="41" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
         <v>445</v>
       </c>
@@ -15597,7 +15600,7 @@
         <v>63.1</v>
       </c>
     </row>
-    <row r="42" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
         <v>446</v>
       </c>
@@ -15611,7 +15614,7 @@
         <v>137.6</v>
       </c>
     </row>
-    <row r="43" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
         <v>447</v>
       </c>
@@ -15628,7 +15631,7 @@
         <v>92.7</v>
       </c>
     </row>
-    <row r="44" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
         <v>448</v>
       </c>
@@ -15645,7 +15648,7 @@
         <v>137.19999999999999</v>
       </c>
     </row>
-    <row r="45" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
         <v>449</v>
       </c>
@@ -15673,13 +15676,13 @@
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0800-000000000000}">
   <dimension ref="A1:K6"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="60.875" customWidth="1"/>
     <col min="2" max="11" width="20.875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>394</v>
       </c>
@@ -15714,7 +15717,7 @@
         <v>458</v>
       </c>
     </row>
-    <row r="2" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>459</v>
       </c>
@@ -15725,7 +15728,7 @@
         <v>460</v>
       </c>
     </row>
-    <row r="3" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>461</v>
       </c>
@@ -15736,7 +15739,7 @@
         <v>460</v>
       </c>
     </row>
-    <row r="4" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>462</v>
       </c>
@@ -15747,7 +15750,7 @@
         <v>460</v>
       </c>
     </row>
-    <row r="5" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>463</v>
       </c>
@@ -15758,7 +15761,7 @@
         <v>460</v>
       </c>
     </row>
-    <row r="6" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>464</v>
       </c>

--- a/bareme_couts.xlsx
+++ b/bareme_couts.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\hateta72d\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C3B7C0C3-33B3-4CB0-A088-F94481C122F3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C22D1911-10F3-406D-BEC8-BC1060757182}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="22932" yWindow="-2136" windowWidth="23256" windowHeight="13896" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="22932" yWindow="-2136" windowWidth="23256" windowHeight="13896" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Lisez-moi" sheetId="1" r:id="rId1"/>
@@ -9587,9 +9587,6 @@
       <c r="F2">
         <v>100.8</v>
       </c>
-      <c r="H2">
-        <v>123456789</v>
-      </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
